--- a/data/jEPlus-LHS/ICAE2026_DataRegistry_P1-P9.xlsx
+++ b/data/jEPlus-LHS/ICAE2026_DataRegistry_P1-P9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8B0343-CFA7-4FC4-9152-05D60473E893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576A593B-EBBD-44CE-9CD2-649B528A87FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -135,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4159" uniqueCount="3574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5206" uniqueCount="4552">
   <si>
     <t>Sym</t>
   </si>
@@ -11709,6 +11709,2940 @@
       <t xml:space="preserve"> EXTERNAL TEST</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulation work directories and results will be stored in: D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\3\</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:33 KST [Local batch simulation controller] Writing job lists to D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\joblist_out.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:33 KST [Local batch simulation controller] Job LHS-000000 started. 149 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:33 KST [Local batch simulation controller] Job LHS-000001 started. 148 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:34 KST [Local batch simulation controller] Job LHS-000002 started. 147 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:34 KST [Local batch simulation controller] Job LHS-000003 started. 146 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:34 KST [Local batch simulation controller] Job LHS-000004 started. 145 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:34 KST [Local batch simulation controller] Job LHS-000005 started. 144 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:34 KST [Local batch simulation controller] Job LHS-000006 started. 143 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:34 KST [Local batch simulation controller] Job LHS-000007 started. 142 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000008 started. 141 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000009 started. 140 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000010 started. 139 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000011 started. 138 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000012 started. 137 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000013 started. 136 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000014 started. 135 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000015 started. 134 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:35 KST [Local batch simulation controller] Job LHS-000016 started. 133 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000017 started. 132 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000018 started. 131 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000019 started. 130 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000020 started. 129 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000021 started. 128 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000022 started. 127 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000023 started. 126 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000024 started. 125 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:36 KST [Local batch simulation controller] Job LHS-000025 started. 124 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:37 KST [Local batch simulation controller] Job LHS-000026 started. 123 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:06:37 KST [Local batch simulation controller] Job LHS-000027 started. 122 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:11 KST [Local batch simulation controller] Job LHS-000028 started. 121 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:12 KST [Local batch simulation controller] Job LHS-000029 started. 120 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:14 KST [Local batch simulation controller] Job LHS-000030 started. 119 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:15 KST [Local batch simulation controller] Job LHS-000031 started. 118 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:16 KST [Local batch simulation controller] Job LHS-000032 started. 117 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:22 KST [Local batch simulation controller] Job LHS-000033 started. 116 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:22 KST [Local batch simulation controller] Job LHS-000034 started. 115 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:22 KST [Local batch simulation controller] Job LHS-000035 started. 114 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:25 KST [Local batch simulation controller] Job LHS-000036 started. 113 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:25 KST [Local batch simulation controller] Job LHS-000037 started. 112 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:26 KST [Local batch simulation controller] Job LHS-000038 started. 111 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:27 KST [Local batch simulation controller] Job LHS-000039 started. 110 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:27 KST [Local batch simulation controller] Job LHS-000040 started. 109 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:28 KST [Local batch simulation controller] Job LHS-000041 started. 108 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:28 KST [Local batch simulation controller] Job LHS-000042 started. 107 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:28 KST [Local batch simulation controller] Job LHS-000043 started. 106 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:29 KST [Local batch simulation controller] Job LHS-000044 started. 105 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:30 KST [Local batch simulation controller] Job LHS-000045 started. 104 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:31 KST [Local batch simulation controller] Job LHS-000046 started. 103 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:33 KST [Local batch simulation controller] Job LHS-000047 started. 102 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:34 KST [Local batch simulation controller] Job LHS-000048 started. 101 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:35 KST [Local batch simulation controller] Job LHS-000049 started. 100 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:36 KST [Local batch simulation controller] Job LHS-000050 started. 99 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:36 KST [Local batch simulation controller] Job LHS-000051 started. 98 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:37 KST [Local batch simulation controller] Job LHS-000052 started. 97 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:43 KST [Local batch simulation controller] Job LHS-000053 started. 96 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:47 KST [Local batch simulation controller] Job LHS-000054 started. 95 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:08:56 KST [Local batch simulation controller] Job LHS-000055 started. 94 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:11:46 KST [Local batch simulation controller] Job LHS-000056 started. 93 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:11:46 KST [Local batch simulation controller] Job LHS-000057 started. 92 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:11:59 KST [Local batch simulation controller] Job LHS-000058 started. 91 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:00 KST [Local batch simulation controller] Job LHS-000059 started. 90 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:15 KST [Local batch simulation controller] Job LHS-000060 started. 89 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:16 KST [Local batch simulation controller] Job LHS-000061 started. 88 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:19 KST [Local batch simulation controller] Job LHS-000062 started. 87 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:19 KST [Local batch simulation controller] Job LHS-000063 started. 86 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:27 KST [Local batch simulation controller] Job LHS-000064 started. 85 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:27 KST [Local batch simulation controller] Job LHS-000065 started. 84 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:28 KST [Local batch simulation controller] Job LHS-000066 started. 83 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:31 KST [Local batch simulation controller] Job LHS-000067 started. 82 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:34 KST [Local batch simulation controller] Job LHS-000068 started. 81 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:34 KST [Local batch simulation controller] Job LHS-000069 started. 80 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:36 KST [Local batch simulation controller] Job LHS-000070 started. 79 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:37 KST [Local batch simulation controller] Job LHS-000071 started. 78 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:41 KST [Local batch simulation controller] Job LHS-000072 started. 77 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:45 KST [Local batch simulation controller] Job LHS-000073 started. 76 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:46 KST [Local batch simulation controller] Job LHS-000074 started. 75 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:47 KST [Local batch simulation controller] Job LHS-000075 started. 74 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:48 KST [Local batch simulation controller] Job LHS-000076 started. 73 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:50 KST [Local batch simulation controller] Job LHS-000077 started. 72 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:51 KST [Local batch simulation controller] Job LHS-000078 started. 71 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:52 KST [Local batch simulation controller] Job LHS-000079 started. 70 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:12:53 KST [Local batch simulation controller] Job LHS-000080 started. 69 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:13:00 KST [Local batch simulation controller] Job LHS-000081 started. 68 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:13:14 KST [Local batch simulation controller] Job LHS-000082 started. 67 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:13:17 KST [Local batch simulation controller] Job LHS-000083 started. 66 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:14:39 KST [Local batch simulation controller] Job LHS-000084 started. 65 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:16 KST [Local batch simulation controller] Job LHS-000085 started. 64 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:24 KST [Local batch simulation controller] Job LHS-000086 started. 63 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:35 KST [Local batch simulation controller] Job LHS-000087 started. 62 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:39 KST [Local batch simulation controller] Job LHS-000088 started. 61 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:42 KST [Local batch simulation controller] Job LHS-000089 started. 60 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:46 KST [Local batch simulation controller] Job LHS-000090 started. 59 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:46 KST [Local batch simulation controller] Job LHS-000091 started. 58 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:46 KST [Local batch simulation controller] Job LHS-000092 started. 57 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:47 KST [Local batch simulation controller] Job LHS-000093 started. 56 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:48 KST [Local batch simulation controller] Job LHS-000094 started. 55 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:58 KST [Local batch simulation controller] Job LHS-000095 started. 54 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:58 KST [Local batch simulation controller] Job LHS-000096 started. 53 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:15:59 KST [Local batch simulation controller] Job LHS-000097 started. 52 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:01 KST [Local batch simulation controller] Job LHS-000098 started. 51 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:11 KST [Local batch simulation controller] Job LHS-000099 started. 50 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:14 KST [Local batch simulation controller] Job LHS-000100 started. 49 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:17 KST [Local batch simulation controller] Job LHS-000101 started. 48 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:17 KST [Local batch simulation controller] Job LHS-000102 started. 47 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:19 KST [Local batch simulation controller] Job LHS-000103 started. 46 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:20 KST [Local batch simulation controller] Job LHS-000104 started. 45 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:22 KST [Local batch simulation controller] Job LHS-000105 started. 44 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:28 KST [Local batch simulation controller] Job LHS-000106 started. 43 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:30 KST [Local batch simulation controller] Job LHS-000107 started. 42 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:32 KST [Local batch simulation controller] Job LHS-000108 started. 41 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:38 KST [Local batch simulation controller] Job LHS-000109 started. 40 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:40 KST [Local batch simulation controller] Job LHS-000110 started. 39 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:16:42 KST [Local batch simulation controller] Job LHS-000111 started. 38 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:13 KST [Local batch simulation controller] Job LHS-000112 started. 37 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:31 KST [Local batch simulation controller] Job LHS-000113 started. 36 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:33 KST [Local batch simulation controller] Job LHS-000114 started. 35 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:36 KST [Local batch simulation controller] Job LHS-000115 started. 34 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:38 KST [Local batch simulation controller] Job LHS-000116 started. 33 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:39 KST [Local batch simulation controller] Job LHS-000117 started. 32 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:42 KST [Local batch simulation controller] Job LHS-000118 started. 31 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:44 KST [Local batch simulation controller] Job LHS-000119 started. 30 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:50 KST [Local batch simulation controller] Job LHS-000120 started. 29 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:51 KST [Local batch simulation controller] Job LHS-000121 started. 28 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:52 KST [Local batch simulation controller] Job LHS-000122 started. 27 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:53 KST [Local batch simulation controller] Job LHS-000123 started. 26 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:57 KST [Local batch simulation controller] Job LHS-000124 started. 25 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:17:57 KST [Local batch simulation controller] Job LHS-000125 started. 24 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:03 KST [Local batch simulation controller] Job LHS-000126 started. 23 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:10 KST [Local batch simulation controller] Job LHS-000127 started. 22 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:10 KST [Local batch simulation controller] Job LHS-000128 started. 21 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:14 KST [Local batch simulation controller] Job LHS-000129 started. 20 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:17 KST [Local batch simulation controller] Job LHS-000130 started. 19 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:18 KST [Local batch simulation controller] Job LHS-000131 started. 18 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:18 KST [Local batch simulation controller] Job LHS-000132 started. 17 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:21 KST [Local batch simulation controller] Job LHS-000133 started. 16 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:23 KST [Local batch simulation controller] Job LHS-000134 started. 15 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:24 KST [Local batch simulation controller] Job LHS-000135 started. 14 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:28 KST [Local batch simulation controller] Job LHS-000136 started. 13 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:30 KST [Local batch simulation controller] Job LHS-000137 started. 12 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:31 KST [Local batch simulation controller] Job LHS-000138 started. 11 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:18:39 KST [Local batch simulation controller] Job LHS-000139 started. 10 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:19:29 KST [Local batch simulation controller] Job LHS-000140 started. 9 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:19:37 KST [Local batch simulation controller] Job LHS-000141 started. 8 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:19:47 KST [Local batch simulation controller] Job LHS-000142 started. 7 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:13 KST [Local batch simulation controller] Job LHS-000143 started. 6 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:17 KST [Local batch simulation controller] Job LHS-000144 started. 5 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:19 KST [Local batch simulation controller] Job LHS-000145 started. 4 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:21 KST [Local batch simulation controller] Job LHS-000146 started. 3 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:25 KST [Local batch simulation controller] Job LHS-000147 started. 2 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:29 KST [Local batch simulation controller] Job LHS-000148 started. 1 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:39 KST [Local batch simulation controller] Job LHS-000149 started. 0 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:20:39 KST [Local batch simulation controller] Nearly there ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:26 KST [Local batch simulation controller] Local batch simulation controller is FINISHED [Que=0, Run=0, Fin=150]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Jul 2026 16:22:26 KST [Local batch simulation controller] Local agent stopped. </t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:26 KST [Local batch simulation controller] Collecting results ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:26 KST [Local batch simulation controller] Standard report collector collected 150 simulation reports in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\3\RunTimes.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:26 KST [Local batch simulation controller] Standard report collector collected job index table in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\3\SimJobIndex.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:29 KST [Local batch simulation controller] Combined result table AllCombinedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:29 KST [Local batch simulation controller] Derivative result table AllDerivedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:29 KST [Local batch simulation controller] All done!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:29 KST [Local batch simulation controller] Simulation finished at: Mon, 6 Jul 2026 16:22:29</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:22:29 KST [Local batch simulation controller] Total execution time = 955 seconds.</t>
+  </si>
+  <si>
+    <t>Simulation work directories and results will be stored in: D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\4\</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:11 KST [Local batch simulation controller] Writing job lists to D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\joblist_out.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:11 KST [Local batch simulation controller] Job LHS-000000 started. 149 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:11 KST [Local batch simulation controller] Job LHS-000001 started. 148 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000002 started. 147 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000003 started. 146 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000004 started. 145 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000005 started. 144 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000006 started. 143 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000007 started. 142 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000008 started. 141 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000009 started. 140 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:12 KST [Local batch simulation controller] Job LHS-000010 started. 139 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000011 started. 138 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000012 started. 137 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000013 started. 136 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000014 started. 135 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000015 started. 134 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000016 started. 133 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000017 started. 132 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000018 started. 131 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000019 started. 130 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:13 KST [Local batch simulation controller] Job LHS-000020 started. 129 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000021 started. 128 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000022 started. 127 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000023 started. 126 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000024 started. 125 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000025 started. 124 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000026 started. 123 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:50:14 KST [Local batch simulation controller] Job LHS-000027 started. 122 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:42 KST [Local batch simulation controller] Job LHS-000028 started. 121 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:42 KST [Local batch simulation controller] Job LHS-000029 started. 120 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:44 KST [Local batch simulation controller] Job LHS-000030 started. 119 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:46 KST [Local batch simulation controller] Job LHS-000031 started. 118 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:47 KST [Local batch simulation controller] Job LHS-000032 started. 117 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:48 KST [Local batch simulation controller] Job LHS-000033 started. 116 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:51 KST [Local batch simulation controller] Job LHS-000034 started. 115 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:53 KST [Local batch simulation controller] Job LHS-000035 started. 114 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:54 KST [Local batch simulation controller] Job LHS-000036 started. 113 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:55 KST [Local batch simulation controller] Job LHS-000037 started. 112 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:58 KST [Local batch simulation controller] Job LHS-000038 started. 111 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:51:59 KST [Local batch simulation controller] Job LHS-000039 started. 110 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:00 KST [Local batch simulation controller] Job LHS-000040 started. 109 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:01 KST [Local batch simulation controller] Job LHS-000041 started. 108 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:02 KST [Local batch simulation controller] Job LHS-000042 started. 107 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:02 KST [Local batch simulation controller] Job LHS-000043 started. 106 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:03 KST [Local batch simulation controller] Job LHS-000044 started. 105 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:04 KST [Local batch simulation controller] Job LHS-000045 started. 104 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:04 KST [Local batch simulation controller] Job LHS-000046 started. 103 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:06 KST [Local batch simulation controller] Job LHS-000047 started. 102 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:07 KST [Local batch simulation controller] Job LHS-000048 started. 101 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:12 KST [Local batch simulation controller] Job LHS-000049 started. 100 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:13 KST [Local batch simulation controller] Job LHS-000050 started. 99 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:14 KST [Local batch simulation controller] Job LHS-000051 started. 98 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:15 KST [Local batch simulation controller] Job LHS-000052 started. 97 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:16 KST [Local batch simulation controller] Job LHS-000053 started. 96 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:17 KST [Local batch simulation controller] Job LHS-000054 started. 95 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:52:19 KST [Local batch simulation controller] Job LHS-000055 started. 94 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:53:47 KST [Local batch simulation controller] Job LHS-000056 started. 93 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:23 KST [Local batch simulation controller] Job LHS-000057 started. 92 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:26 KST [Local batch simulation controller] Job LHS-000058 started. 91 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:35 KST [Local batch simulation controller] Job LHS-000059 started. 90 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:42 KST [Local batch simulation controller] Job LHS-000060 started. 89 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:44 KST [Local batch simulation controller] Job LHS-000061 started. 88 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:44 KST [Local batch simulation controller] Job LHS-000062 started. 87 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:46 KST [Local batch simulation controller] Job LHS-000063 started. 86 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:50 KST [Local batch simulation controller] Job LHS-000064 started. 85 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:53 KST [Local batch simulation controller] Job LHS-000065 started. 84 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:54:53 KST [Local batch simulation controller] Job LHS-000066 started. 83 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:02 KST [Local batch simulation controller] Job LHS-000067 started. 82 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:08 KST [Local batch simulation controller] Job LHS-000068 started. 81 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:18 KST [Local batch simulation controller] Job LHS-000069 started. 80 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:22 KST [Local batch simulation controller] Job LHS-000070 started. 79 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:25 KST [Local batch simulation controller] Job LHS-000071 started. 78 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:28 KST [Local batch simulation controller] Job LHS-000072 started. 77 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:32 KST [Local batch simulation controller] Job LHS-000073 started. 76 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:35 KST [Local batch simulation controller] Job LHS-000074 started. 75 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:39 KST [Local batch simulation controller] Job LHS-000075 started. 74 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:46 KST [Local batch simulation controller] Job LHS-000076 started. 73 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:49 KST [Local batch simulation controller] Job LHS-000077 started. 72 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:52 KST [Local batch simulation controller] Job LHS-000078 started. 71 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:55:55 KST [Local batch simulation controller] Job LHS-000079 started. 70 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:56:07 KST [Local batch simulation controller] Job LHS-000080 started. 69 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:56:08 KST [Local batch simulation controller] Job LHS-000081 started. 68 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:56:13 KST [Local batch simulation controller] Job LHS-000082 started. 67 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:56:21 KST [Local batch simulation controller] Job LHS-000083 started. 66 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:56:41 KST [Local batch simulation controller] Job LHS-000084 started. 65 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:57:52 KST [Local batch simulation controller] Job LHS-000085 started. 64 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:04 KST [Local batch simulation controller] Job LHS-000086 started. 63 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:12 KST [Local batch simulation controller] Job LHS-000087 started. 62 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:12 KST [Local batch simulation controller] Job LHS-000088 started. 61 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:12 KST [Local batch simulation controller] Job LHS-000089 started. 60 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:15 KST [Local batch simulation controller] Job LHS-000090 started. 59 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:17 KST [Local batch simulation controller] Job LHS-000091 started. 58 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:21 KST [Local batch simulation controller] Job LHS-000092 started. 57 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:24 KST [Local batch simulation controller] Job LHS-000093 started. 56 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:26 KST [Local batch simulation controller] Job LHS-000094 started. 55 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:27 KST [Local batch simulation controller] Job LHS-000095 started. 54 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:27 KST [Local batch simulation controller] Job LHS-000096 started. 53 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:28 KST [Local batch simulation controller] Job LHS-000097 started. 52 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:30 KST [Local batch simulation controller] Job LHS-000098 started. 51 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:32 KST [Local batch simulation controller] Job LHS-000099 started. 50 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:35 KST [Local batch simulation controller] Job LHS-000100 started. 49 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:43 KST [Local batch simulation controller] Job LHS-000101 started. 48 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:45 KST [Local batch simulation controller] Job LHS-000102 started. 47 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:46 KST [Local batch simulation controller] Job LHS-000103 started. 46 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:46 KST [Local batch simulation controller] Job LHS-000104 started. 45 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:52 KST [Local batch simulation controller] Job LHS-000105 started. 44 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:58:53 KST [Local batch simulation controller] Job LHS-000106 started. 43 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:00 KST [Local batch simulation controller] Job LHS-000107 started. 42 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:00 KST [Local batch simulation controller] Job LHS-000108 started. 41 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:01 KST [Local batch simulation controller] Job LHS-000109 started. 40 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:10 KST [Local batch simulation controller] Job LHS-000110 started. 39 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:12 KST [Local batch simulation controller] Job LHS-000111 started. 38 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:15 KST [Local batch simulation controller] Job LHS-000112 started. 37 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:46 KST [Local batch simulation controller] Job LHS-000113 started. 36 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:53 KST [Local batch simulation controller] Job LHS-000114 started. 35 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:58 KST [Local batch simulation controller] Job LHS-000115 started. 34 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 16:59:59 KST [Local batch simulation controller] Job LHS-000116 started. 33 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:08 KST [Local batch simulation controller] Job LHS-000117 started. 32 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:13 KST [Local batch simulation controller] Job LHS-000118 started. 31 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:13 KST [Local batch simulation controller] Job LHS-000119 started. 30 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:13 KST [Local batch simulation controller] Job LHS-000120 started. 29 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:14 KST [Local batch simulation controller] Job LHS-000121 started. 28 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:15 KST [Local batch simulation controller] Job LHS-000122 started. 27 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:16 KST [Local batch simulation controller] Job LHS-000123 started. 26 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:17 KST [Local batch simulation controller] Job LHS-000124 started. 25 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:19 KST [Local batch simulation controller] Job LHS-000125 started. 24 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:20 KST [Local batch simulation controller] Job LHS-000126 started. 23 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:23 KST [Local batch simulation controller] Job LHS-000127 started. 22 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:24 KST [Local batch simulation controller] Job LHS-000128 started. 21 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:24 KST [Local batch simulation controller] Job LHS-000129 started. 20 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:32 KST [Local batch simulation controller] Job LHS-000130 started. 19 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:34 KST [Local batch simulation controller] Job LHS-000131 started. 18 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:41 KST [Local batch simulation controller] Job LHS-000132 started. 17 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:44 KST [Local batch simulation controller] Job LHS-000133 started. 16 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:49 KST [Local batch simulation controller] Job LHS-000134 started. 15 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:49 KST [Local batch simulation controller] Job LHS-000135 started. 14 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:54 KST [Local batch simulation controller] Job LHS-000136 started. 13 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:55 KST [Local batch simulation controller] Job LHS-000137 started. 12 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:58 KST [Local batch simulation controller] Job LHS-000138 started. 11 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:00:59 KST [Local batch simulation controller] Job LHS-000139 started. 10 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:01:08 KST [Local batch simulation controller] Job LHS-000140 started. 9 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:01:30 KST [Local batch simulation controller] Job LHS-000141 started. 8 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:01:44 KST [Local batch simulation controller] Job LHS-000142 started. 7 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:01:44 KST [Local batch simulation controller] Job LHS-000143 started. 6 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:01:59 KST [Local batch simulation controller] Job LHS-000144 started. 5 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:01:59 KST [Local batch simulation controller] Job LHS-000145 started. 4 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:02:05 KST [Local batch simulation controller] Job LHS-000146 started. 3 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:02:09 KST [Local batch simulation controller] Job LHS-000147 started. 2 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:02:12 KST [Local batch simulation controller] Job LHS-000148 started. 1 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:02:12 KST [Local batch simulation controller] Job LHS-000149 started. 0 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:02:12 KST [Local batch simulation controller] Nearly there ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:20 KST [Local batch simulation controller] Local batch simulation controller is FINISHED [Que=0, Run=0, Fin=150]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Jul 2026 17:03:20 KST [Local batch simulation controller] Local agent stopped. </t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:20 KST [Local batch simulation controller] Collecting results ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:20 KST [Local batch simulation controller] Standard report collector collected 150 simulation reports in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\4\RunTimes.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:20 KST [Local batch simulation controller] Standard report collector collected job index table in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\4\SimJobIndex.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:23 KST [Local batch simulation controller] Combined result table AllCombinedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:23 KST [Local batch simulation controller] Derivative result table AllDerivedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:23 KST [Local batch simulation controller] All done!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:23 KST [Local batch simulation controller] Simulation finished at: Mon, 6 Jul 2026 17:03:23</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:03:23 KST [Local batch simulation controller] Total execution time = 791 seconds.</t>
+  </si>
+  <si>
+    <t>Simulation work directories and results will be stored in: D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\6\</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:41 KST [Local batch simulation controller] Writing job lists to D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\joblist_out.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:41 KST [Local batch simulation controller] Job LHS-000000 started. 149 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:41 KST [Local batch simulation controller] Job LHS-000001 started. 148 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000002 started. 147 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000003 started. 146 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000004 started. 145 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000005 started. 144 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000006 started. 143 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000007 started. 142 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:42 KST [Local batch simulation controller] Job LHS-000008 started. 141 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000009 started. 140 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000010 started. 139 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000011 started. 138 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000012 started. 137 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000013 started. 136 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000014 started. 135 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000015 started. 134 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000016 started. 133 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:43 KST [Local batch simulation controller] Job LHS-000017 started. 132 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000018 started. 131 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000019 started. 130 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000020 started. 129 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000021 started. 128 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000022 started. 127 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000023 started. 126 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000024 started. 125 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000025 started. 124 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000026 started. 123 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:11:44 KST [Local batch simulation controller] Job LHS-000027 started. 122 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:08 KST [Local batch simulation controller] Job LHS-000028 started. 121 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:13 KST [Local batch simulation controller] Job LHS-000029 started. 120 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:15 KST [Local batch simulation controller] Job LHS-000030 started. 119 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:16 KST [Local batch simulation controller] Job LHS-000031 started. 118 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:20 KST [Local batch simulation controller] Job LHS-000032 started. 117 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:23 KST [Local batch simulation controller] Job LHS-000033 started. 116 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:24 KST [Local batch simulation controller] Job LHS-000034 started. 115 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:28 KST [Local batch simulation controller] Job LHS-000035 started. 114 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:30 KST [Local batch simulation controller] Job LHS-000036 started. 113 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:31 KST [Local batch simulation controller] Job LHS-000037 started. 112 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:31 KST [Local batch simulation controller] Job LHS-000038 started. 111 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:31 KST [Local batch simulation controller] Job LHS-000039 started. 110 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:32 KST [Local batch simulation controller] Job LHS-000040 started. 109 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:33 KST [Local batch simulation controller] Job LHS-000041 started. 108 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:33 KST [Local batch simulation controller] Job LHS-000042 started. 107 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:33 KST [Local batch simulation controller] Job LHS-000043 started. 106 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:34 KST [Local batch simulation controller] Job LHS-000044 started. 105 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:34 KST [Local batch simulation controller] Job LHS-000045 started. 104 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:34 KST [Local batch simulation controller] Job LHS-000046 started. 103 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:35 KST [Local batch simulation controller] Job LHS-000047 started. 102 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:35 KST [Local batch simulation controller] Job LHS-000048 started. 101 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:36 KST [Local batch simulation controller] Job LHS-000049 started. 100 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:37 KST [Local batch simulation controller] Job LHS-000050 started. 99 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:39 KST [Local batch simulation controller] Job LHS-000051 started. 98 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:39 KST [Local batch simulation controller] Job LHS-000052 started. 97 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:41 KST [Local batch simulation controller] Job LHS-000053 started. 96 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:43 KST [Local batch simulation controller] Job LHS-000054 started. 95 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:13:46 KST [Local batch simulation controller] Job LHS-000055 started. 94 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:14:41 KST [Local batch simulation controller] Job LHS-000056 started. 93 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:14:47 KST [Local batch simulation controller] Job LHS-000057 started. 92 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:14:55 KST [Local batch simulation controller] Job LHS-000058 started. 91 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:00 KST [Local batch simulation controller] Job LHS-000059 started. 90 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:12 KST [Local batch simulation controller] Job LHS-000060 started. 89 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:12 KST [Local batch simulation controller] Job LHS-000061 started. 88 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:14 KST [Local batch simulation controller] Job LHS-000062 started. 87 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:15 KST [Local batch simulation controller] Job LHS-000063 started. 86 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:17 KST [Local batch simulation controller] Job LHS-000064 started. 85 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:19 KST [Local batch simulation controller] Job LHS-000065 started. 84 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:20 KST [Local batch simulation controller] Job LHS-000066 started. 83 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:20 KST [Local batch simulation controller] Job LHS-000067 started. 82 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:21 KST [Local batch simulation controller] Job LHS-000068 started. 81 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:21 KST [Local batch simulation controller] Job LHS-000069 started. 80 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:21 KST [Local batch simulation controller] Job LHS-000070 started. 79 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:21 KST [Local batch simulation controller] Job LHS-000071 started. 78 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:23 KST [Local batch simulation controller] Job LHS-000072 started. 77 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:23 KST [Local batch simulation controller] Job LHS-000073 started. 76 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:24 KST [Local batch simulation controller] Job LHS-000074 started. 75 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:25 KST [Local batch simulation controller] Job LHS-000075 started. 74 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:25 KST [Local batch simulation controller] Job LHS-000076 started. 73 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:28 KST [Local batch simulation controller] Job LHS-000077 started. 72 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:32 KST [Local batch simulation controller] Job LHS-000078 started. 71 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:33 KST [Local batch simulation controller] Job LHS-000079 started. 70 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:35 KST [Local batch simulation controller] Job LHS-000080 started. 69 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:36 KST [Local batch simulation controller] Job LHS-000081 started. 68 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:37 KST [Local batch simulation controller] Job LHS-000082 started. 67 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:15:42 KST [Local batch simulation controller] Job LHS-000083 started. 66 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:16:36 KST [Local batch simulation controller] Job LHS-000084 started. 65 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:16:48 KST [Local batch simulation controller] Job LHS-000085 started. 64 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:16:49 KST [Local batch simulation controller] Job LHS-000086 started. 63 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:16:54 KST [Local batch simulation controller] Job LHS-000087 started. 62 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:16:54 KST [Local batch simulation controller] Job LHS-000088 started. 61 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:05 KST [Local batch simulation controller] Job LHS-000089 started. 60 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:07 KST [Local batch simulation controller] Job LHS-000090 started. 59 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:11 KST [Local batch simulation controller] Job LHS-000091 started. 58 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:17 KST [Local batch simulation controller] Job LHS-000092 started. 57 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:18 KST [Local batch simulation controller] Job LHS-000093 started. 56 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:18 KST [Local batch simulation controller] Job LHS-000094 started. 55 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:21 KST [Local batch simulation controller] Job LHS-000095 started. 54 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:28 KST [Local batch simulation controller] Job LHS-000096 started. 53 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:29 KST [Local batch simulation controller] Job LHS-000097 started. 52 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:32 KST [Local batch simulation controller] Job LHS-000098 started. 51 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:36 KST [Local batch simulation controller] Job LHS-000099 started. 50 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:37 KST [Local batch simulation controller] Job LHS-000100 started. 49 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:38 KST [Local batch simulation controller] Job LHS-000101 started. 48 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:38 KST [Local batch simulation controller] Job LHS-000102 started. 47 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:43 KST [Local batch simulation controller] Job LHS-000103 started. 46 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:45 KST [Local batch simulation controller] Job LHS-000104 started. 45 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:45 KST [Local batch simulation controller] Job LHS-000105 started. 44 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:47 KST [Local batch simulation controller] Job LHS-000106 started. 43 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:48 KST [Local batch simulation controller] Job LHS-000107 started. 42 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:49 KST [Local batch simulation controller] Job LHS-000108 started. 41 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:17:57 KST [Local batch simulation controller] Job LHS-000109 started. 40 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:04 KST [Local batch simulation controller] Job LHS-000110 started. 39 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:16 KST [Local batch simulation controller] Job LHS-000111 started. 38 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:17 KST [Local batch simulation controller] Job LHS-000112 started. 37 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:19 KST [Local batch simulation controller] Job LHS-000113 started. 36 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:25 KST [Local batch simulation controller] Job LHS-000114 started. 35 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:54 KST [Local batch simulation controller] Job LHS-000115 started. 34 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:18:57 KST [Local batch simulation controller] Job LHS-000116 started. 33 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:05 KST [Local batch simulation controller] Job LHS-000117 started. 32 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:12 KST [Local batch simulation controller] Job LHS-000118 started. 31 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:14 KST [Local batch simulation controller] Job LHS-000119 started. 30 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:14 KST [Local batch simulation controller] Job LHS-000120 started. 29 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:14 KST [Local batch simulation controller] Job LHS-000121 started. 28 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:18 KST [Local batch simulation controller] Job LHS-000122 started. 27 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:22 KST [Local batch simulation controller] Job LHS-000123 started. 26 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:23 KST [Local batch simulation controller] Job LHS-000124 started. 25 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:28 KST [Local batch simulation controller] Job LHS-000125 started. 24 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:30 KST [Local batch simulation controller] Job LHS-000126 started. 23 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:31 KST [Local batch simulation controller] Job LHS-000127 started. 22 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:31 KST [Local batch simulation controller] Job LHS-000128 started. 21 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:32 KST [Local batch simulation controller] Job LHS-000129 started. 20 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:33 KST [Local batch simulation controller] Job LHS-000130 started. 19 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:38 KST [Local batch simulation controller] Job LHS-000131 started. 18 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:39 KST [Local batch simulation controller] Job LHS-000132 started. 17 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:46 KST [Local batch simulation controller] Job LHS-000133 started. 16 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:47 KST [Local batch simulation controller] Job LHS-000134 started. 15 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:47 KST [Local batch simulation controller] Job LHS-000135 started. 14 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:47 KST [Local batch simulation controller] Job LHS-000136 started. 13 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:50 KST [Local batch simulation controller] Job LHS-000137 started. 12 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:55 KST [Local batch simulation controller] Job LHS-000138 started. 11 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:19:56 KST [Local batch simulation controller] Job LHS-000139 started. 10 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:00 KST [Local batch simulation controller] Job LHS-000140 started. 9 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:02 KST [Local batch simulation controller] Job LHS-000141 started. 8 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:12 KST [Local batch simulation controller] Job LHS-000142 started. 7 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:43 KST [Local batch simulation controller] Job LHS-000143 started. 6 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:48 KST [Local batch simulation controller] Job LHS-000144 started. 5 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:53 KST [Local batch simulation controller] Job LHS-000145 started. 4 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:20:58 KST [Local batch simulation controller] Job LHS-000146 started. 3 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:04 KST [Local batch simulation controller] Job LHS-000147 started. 2 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:06 KST [Local batch simulation controller] Job LHS-000148 started. 1 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:08 KST [Local batch simulation controller] Job LHS-000149 started. 0 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:08 KST [Local batch simulation controller] Nearly there ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:58 KST [Local batch simulation controller] Local batch simulation controller is FINISHED [Que=0, Run=0, Fin=150]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Jul 2026 17:21:58 KST [Local batch simulation controller] Local agent stopped. </t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:58 KST [Local batch simulation controller] Collecting results ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:58 KST [Local batch simulation controller] Standard report collector collected 150 simulation reports in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\6\RunTimes.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:21:58 KST [Local batch simulation controller] Standard report collector collected job index table in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\6\SimJobIndex.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:22:01 KST [Local batch simulation controller] Combined result table AllCombinedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:22:01 KST [Local batch simulation controller] Derivative result table AllDerivedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:22:01 KST [Local batch simulation controller] All done!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:22:01 KST [Local batch simulation controller] Simulation finished at: Mon, 6 Jul 2026 17:22:01</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:22:01 KST [Local batch simulation controller] Total execution time = 620 seconds.</t>
+  </si>
+  <si>
+    <t>Simulation work directories and results will be stored in: D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\7\</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:29 KST [Local batch simulation controller] Writing job lists to D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\joblist_out.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:29 KST [Local batch simulation controller] Job LHS-000000 started. 149 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:29 KST [Local batch simulation controller] Job LHS-000001 started. 148 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:30 KST [Local batch simulation controller] Job LHS-000002 started. 147 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:30 KST [Local batch simulation controller] Job LHS-000003 started. 146 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:30 KST [Local batch simulation controller] Job LHS-000004 started. 145 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:30 KST [Local batch simulation controller] Job LHS-000005 started. 144 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000006 started. 143 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000007 started. 142 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000008 started. 141 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000009 started. 140 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000010 started. 139 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000011 started. 138 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000012 started. 137 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000013 started. 136 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:31 KST [Local batch simulation controller] Job LHS-000014 started. 135 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000015 started. 134 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000016 started. 133 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000017 started. 132 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000018 started. 131 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000019 started. 130 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000020 started. 129 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000021 started. 128 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000022 started. 127 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:32 KST [Local batch simulation controller] Job LHS-000023 started. 126 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:33 KST [Local batch simulation controller] Job LHS-000024 started. 125 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:33 KST [Local batch simulation controller] Job LHS-000025 started. 124 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:33 KST [Local batch simulation controller] Job LHS-000026 started. 123 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:23:33 KST [Local batch simulation controller] Job LHS-000027 started. 122 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:24:58 KST [Local batch simulation controller] Job LHS-000028 started. 121 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:00 KST [Local batch simulation controller] Job LHS-000029 started. 120 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:03 KST [Local batch simulation controller] Job LHS-000030 started. 119 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:05 KST [Local batch simulation controller] Job LHS-000031 started. 118 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:06 KST [Local batch simulation controller] Job LHS-000032 started. 117 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:12 KST [Local batch simulation controller] Job LHS-000033 started. 116 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:12 KST [Local batch simulation controller] Job LHS-000034 started. 115 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:12 KST [Local batch simulation controller] Job LHS-000035 started. 114 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:13 KST [Local batch simulation controller] Job LHS-000036 started. 113 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:13 KST [Local batch simulation controller] Job LHS-000037 started. 112 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:14 KST [Local batch simulation controller] Job LHS-000038 started. 111 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:15 KST [Local batch simulation controller] Job LHS-000039 started. 110 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:15 KST [Local batch simulation controller] Job LHS-000040 started. 109 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:15 KST [Local batch simulation controller] Job LHS-000041 started. 108 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:15 KST [Local batch simulation controller] Job LHS-000042 started. 107 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:16 KST [Local batch simulation controller] Job LHS-000043 started. 106 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:16 KST [Local batch simulation controller] Job LHS-000044 started. 105 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:16 KST [Local batch simulation controller] Job LHS-000045 started. 104 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:18 KST [Local batch simulation controller] Job LHS-000046 started. 103 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:18 KST [Local batch simulation controller] Job LHS-000047 started. 102 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:19 KST [Local batch simulation controller] Job LHS-000048 started. 101 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:19 KST [Local batch simulation controller] Job LHS-000049 started. 100 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:20 KST [Local batch simulation controller] Job LHS-000050 started. 99 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:21 KST [Local batch simulation controller] Job LHS-000051 started. 98 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:22 KST [Local batch simulation controller] Job LHS-000052 started. 97 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:23 KST [Local batch simulation controller] Job LHS-000053 started. 96 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:24 KST [Local batch simulation controller] Job LHS-000054 started. 95 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:25:29 KST [Local batch simulation controller] Job LHS-000055 started. 94 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:44 KST [Local batch simulation controller] Job LHS-000056 started. 93 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:45 KST [Local batch simulation controller] Job LHS-000057 started. 92 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:48 KST [Local batch simulation controller] Job LHS-000058 started. 91 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:48 KST [Local batch simulation controller] Job LHS-000059 started. 90 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:49 KST [Local batch simulation controller] Job LHS-000060 started. 89 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:54 KST [Local batch simulation controller] Job LHS-000061 started. 88 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:55 KST [Local batch simulation controller] Job LHS-000062 started. 87 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:55 KST [Local batch simulation controller] Job LHS-000063 started. 86 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:57 KST [Local batch simulation controller] Job LHS-000064 started. 85 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:57 KST [Local batch simulation controller] Job LHS-000065 started. 84 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:26:58 KST [Local batch simulation controller] Job LHS-000066 started. 83 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:02 KST [Local batch simulation controller] Job LHS-000067 started. 82 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:04 KST [Local batch simulation controller] Job LHS-000068 started. 81 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:05 KST [Local batch simulation controller] Job LHS-000069 started. 80 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:05 KST [Local batch simulation controller] Job LHS-000070 started. 79 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:06 KST [Local batch simulation controller] Job LHS-000071 started. 78 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:08 KST [Local batch simulation controller] Job LHS-000072 started. 77 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:08 KST [Local batch simulation controller] Job LHS-000073 started. 76 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:08 KST [Local batch simulation controller] Job LHS-000074 started. 75 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:09 KST [Local batch simulation controller] Job LHS-000075 started. 74 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:09 KST [Local batch simulation controller] Job LHS-000076 started. 73 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:10 KST [Local batch simulation controller] Job LHS-000077 started. 72 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:10 KST [Local batch simulation controller] Job LHS-000078 started. 71 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:15 KST [Local batch simulation controller] Job LHS-000079 started. 70 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:15 KST [Local batch simulation controller] Job LHS-000080 started. 69 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:19 KST [Local batch simulation controller] Job LHS-000081 started. 68 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:26 KST [Local batch simulation controller] Job LHS-000082 started. 67 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:27:28 KST [Local batch simulation controller] Job LHS-000083 started. 66 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:25 KST [Local batch simulation controller] Job LHS-000084 started. 65 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:25 KST [Local batch simulation controller] Job LHS-000085 started. 64 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:26 KST [Local batch simulation controller] Job LHS-000086 started. 63 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:33 KST [Local batch simulation controller] Job LHS-000087 started. 62 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:33 KST [Local batch simulation controller] Job LHS-000088 started. 61 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:34 KST [Local batch simulation controller] Job LHS-000089 started. 60 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:36 KST [Local batch simulation controller] Job LHS-000090 started. 59 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:38 KST [Local batch simulation controller] Job LHS-000091 started. 58 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:38 KST [Local batch simulation controller] Job LHS-000092 started. 57 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:42 KST [Local batch simulation controller] Job LHS-000093 started. 56 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:43 KST [Local batch simulation controller] Job LHS-000094 started. 55 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:45 KST [Local batch simulation controller] Job LHS-000095 started. 54 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:49 KST [Local batch simulation controller] Job LHS-000096 started. 53 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:52 KST [Local batch simulation controller] Job LHS-000097 started. 52 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:54 KST [Local batch simulation controller] Job LHS-000098 started. 51 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:55 KST [Local batch simulation controller] Job LHS-000099 started. 50 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:56 KST [Local batch simulation controller] Job LHS-000100 started. 49 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:57 KST [Local batch simulation controller] Job LHS-000101 started. 48 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:28:59 KST [Local batch simulation controller] Job LHS-000102 started. 47 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:00 KST [Local batch simulation controller] Job LHS-000103 started. 46 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:00 KST [Local batch simulation controller] Job LHS-000104 started. 45 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:01 KST [Local batch simulation controller] Job LHS-000105 started. 44 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:05 KST [Local batch simulation controller] Job LHS-000106 started. 43 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:09 KST [Local batch simulation controller] Job LHS-000107 started. 42 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:11 KST [Local batch simulation controller] Job LHS-000108 started. 41 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:15 KST [Local batch simulation controller] Job LHS-000109 started. 40 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:18 KST [Local batch simulation controller] Job LHS-000110 started. 39 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:29:19 KST [Local batch simulation controller] Job LHS-000111 started. 38 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:04 KST [Local batch simulation controller] Job LHS-000112 started. 37 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:07 KST [Local batch simulation controller] Job LHS-000113 started. 36 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:17 KST [Local batch simulation controller] Job LHS-000114 started. 35 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:19 KST [Local batch simulation controller] Job LHS-000115 started. 34 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:20 KST [Local batch simulation controller] Job LHS-000116 started. 33 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:26 KST [Local batch simulation controller] Job LHS-000117 started. 32 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:28 KST [Local batch simulation controller] Job LHS-000118 started. 31 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:28 KST [Local batch simulation controller] Job LHS-000119 started. 30 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:28 KST [Local batch simulation controller] Job LHS-000120 started. 29 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:30 KST [Local batch simulation controller] Job LHS-000121 started. 28 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:32 KST [Local batch simulation controller] Job LHS-000122 started. 27 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:35 KST [Local batch simulation controller] Job LHS-000123 started. 26 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:37 KST [Local batch simulation controller] Job LHS-000124 started. 25 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:39 KST [Local batch simulation controller] Job LHS-000125 started. 24 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:40 KST [Local batch simulation controller] Job LHS-000126 started. 23 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:41 KST [Local batch simulation controller] Job LHS-000127 started. 22 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:41 KST [Local batch simulation controller] Job LHS-000128 started. 21 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:43 KST [Local batch simulation controller] Job LHS-000129 started. 20 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:47 KST [Local batch simulation controller] Job LHS-000130 started. 19 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:49 KST [Local batch simulation controller] Job LHS-000131 started. 18 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:53 KST [Local batch simulation controller] Job LHS-000132 started. 17 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:30:58 KST [Local batch simulation controller] Job LHS-000133 started. 16 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:00 KST [Local batch simulation controller] Job LHS-000134 started. 15 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:01 KST [Local batch simulation controller] Job LHS-000135 started. 14 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:01 KST [Local batch simulation controller] Job LHS-000136 started. 13 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:02 KST [Local batch simulation controller] Job LHS-000137 started. 12 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:08 KST [Local batch simulation controller] Job LHS-000138 started. 11 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:19 KST [Local batch simulation controller] Job LHS-000139 started. 10 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:40 KST [Local batch simulation controller] Job LHS-000140 started. 9 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:31:58 KST [Local batch simulation controller] Job LHS-000141 started. 8 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:12 KST [Local batch simulation controller] Job LHS-000142 started. 7 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:15 KST [Local batch simulation controller] Job LHS-000143 started. 6 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:16 KST [Local batch simulation controller] Job LHS-000144 started. 5 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:19 KST [Local batch simulation controller] Job LHS-000145 started. 4 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:20 KST [Local batch simulation controller] Job LHS-000146 started. 3 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:20 KST [Local batch simulation controller] Job LHS-000147 started. 2 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:21 KST [Local batch simulation controller] Job LHS-000148 started. 1 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:23 KST [Local batch simulation controller] Job LHS-000149 started. 0 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:32:24 KST [Local batch simulation controller] Nearly there ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:21 KST [Local batch simulation controller] Local batch simulation controller is FINISHED [Que=0, Run=0, Fin=150]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Jul 2026 17:33:21 KST [Local batch simulation controller] Local agent stopped. </t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:21 KST [Local batch simulation controller] Collecting results ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:22 KST [Local batch simulation controller] Standard report collector collected 150 simulation reports in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\7\RunTimes.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:22 KST [Local batch simulation controller] Standard report collector collected job index table in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\7\SimJobIndex.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:25 KST [Local batch simulation controller] Combined result table AllCombinedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:25 KST [Local batch simulation controller] Derivative result table AllDerivedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:25 KST [Local batch simulation controller] All done!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:25 KST [Local batch simulation controller] Simulation finished at: Mon, 6 Jul 2026 17:33:25</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 17:33:25 KST [Local batch simulation controller] Total execution time = 595 seconds.</t>
+  </si>
+  <si>
+    <t>Simulation work directories and results will be stored in: D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\8\</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:49 KST [Local batch simulation controller] Writing job lists to D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\joblist_out.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:49 KST [Local batch simulation controller] Job LHS-000000 started. 149 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:49 KST [Local batch simulation controller] Job LHS-000001 started. 148 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000002 started. 147 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000003 started. 146 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000004 started. 145 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000005 started. 144 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000006 started. 143 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000007 started. 142 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000008 started. 141 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000009 started. 140 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:50 KST [Local batch simulation controller] Job LHS-000010 started. 139 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000011 started. 138 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000012 started. 137 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000013 started. 136 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000014 started. 135 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000015 started. 134 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000016 started. 133 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000017 started. 132 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000018 started. 131 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000019 started. 130 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:51 KST [Local batch simulation controller] Job LHS-000020 started. 129 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000021 started. 128 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000022 started. 127 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000023 started. 126 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000024 started. 125 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000025 started. 124 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000026 started. 123 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:28:52 KST [Local batch simulation controller] Job LHS-000027 started. 122 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:22 KST [Local batch simulation controller] Job LHS-000028 started. 121 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:23 KST [Local batch simulation controller] Job LHS-000029 started. 120 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:23 KST [Local batch simulation controller] Job LHS-000030 started. 119 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:27 KST [Local batch simulation controller] Job LHS-000031 started. 118 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:28 KST [Local batch simulation controller] Job LHS-000032 started. 117 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:28 KST [Local batch simulation controller] Job LHS-000033 started. 116 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:30 KST [Local batch simulation controller] Job LHS-000034 started. 115 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:31 KST [Local batch simulation controller] Job LHS-000035 started. 114 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:31 KST [Local batch simulation controller] Job LHS-000036 started. 113 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:34 KST [Local batch simulation controller] Job LHS-000037 started. 112 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:34 KST [Local batch simulation controller] Job LHS-000038 started. 111 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:35 KST [Local batch simulation controller] Job LHS-000039 started. 110 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:37 KST [Local batch simulation controller] Job LHS-000040 started. 109 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:38 KST [Local batch simulation controller] Job LHS-000041 started. 108 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:39 KST [Local batch simulation controller] Job LHS-000042 started. 107 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:39 KST [Local batch simulation controller] Job LHS-000043 started. 106 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:40 KST [Local batch simulation controller] Job LHS-000044 started. 105 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:41 KST [Local batch simulation controller] Job LHS-000045 started. 104 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:41 KST [Local batch simulation controller] Job LHS-000046 started. 103 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:42 KST [Local batch simulation controller] Job LHS-000047 started. 102 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:43 KST [Local batch simulation controller] Job LHS-000048 started. 101 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:44 KST [Local batch simulation controller] Job LHS-000049 started. 100 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:45 KST [Local batch simulation controller] Job LHS-000050 started. 99 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:45 KST [Local batch simulation controller] Job LHS-000051 started. 98 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:46 KST [Local batch simulation controller] Job LHS-000052 started. 97 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:47 KST [Local batch simulation controller] Job LHS-000053 started. 96 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:30:49 KST [Local batch simulation controller] Job LHS-000054 started. 95 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:31:00 KST [Local batch simulation controller] Job LHS-000055 started. 94 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:31:53 KST [Local batch simulation controller] Job LHS-000056 started. 93 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:02 KST [Local batch simulation controller] Job LHS-000057 started. 92 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:05 KST [Local batch simulation controller] Job LHS-000058 started. 91 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:06 KST [Local batch simulation controller] Job LHS-000059 started. 90 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:14 KST [Local batch simulation controller] Job LHS-000060 started. 89 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:16 KST [Local batch simulation controller] Job LHS-000061 started. 88 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:16 KST [Local batch simulation controller] Job LHS-000062 started. 87 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:20 KST [Local batch simulation controller] Job LHS-000063 started. 86 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:21 KST [Local batch simulation controller] Job LHS-000064 started. 85 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:22 KST [Local batch simulation controller] Job LHS-000065 started. 84 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:22 KST [Local batch simulation controller] Job LHS-000066 started. 83 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:23 KST [Local batch simulation controller] Job LHS-000067 started. 82 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:23 KST [Local batch simulation controller] Job LHS-000068 started. 81 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:27 KST [Local batch simulation controller] Job LHS-000069 started. 80 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:28 KST [Local batch simulation controller] Job LHS-000070 started. 79 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:34 KST [Local batch simulation controller] Job LHS-000071 started. 78 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:34 KST [Local batch simulation controller] Job LHS-000072 started. 77 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:36 KST [Local batch simulation controller] Job LHS-000073 started. 76 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:37 KST [Local batch simulation controller] Job LHS-000074 started. 75 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:37 KST [Local batch simulation controller] Job LHS-000075 started. 74 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:38 KST [Local batch simulation controller] Job LHS-000076 started. 73 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:38 KST [Local batch simulation controller] Job LHS-000077 started. 72 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:42 KST [Local batch simulation controller] Job LHS-000078 started. 71 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:43 KST [Local batch simulation controller] Job LHS-000079 started. 70 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:45 KST [Local batch simulation controller] Job LHS-000080 started. 69 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:46 KST [Local batch simulation controller] Job LHS-000081 started. 68 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:46 KST [Local batch simulation controller] Job LHS-000082 started. 67 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:32:48 KST [Local batch simulation controller] Job LHS-000083 started. 66 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:33:30 KST [Local batch simulation controller] Job LHS-000084 started. 65 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:33:44 KST [Local batch simulation controller] Job LHS-000085 started. 64 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:33:57 KST [Local batch simulation controller] Job LHS-000086 started. 63 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:33:57 KST [Local batch simulation controller] Job LHS-000087 started. 62 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:01 KST [Local batch simulation controller] Job LHS-000088 started. 61 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:03 KST [Local batch simulation controller] Job LHS-000089 started. 60 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:03 KST [Local batch simulation controller] Job LHS-000090 started. 59 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:07 KST [Local batch simulation controller] Job LHS-000091 started. 58 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:11 KST [Local batch simulation controller] Job LHS-000092 started. 57 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:13 KST [Local batch simulation controller] Job LHS-000093 started. 56 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:19 KST [Local batch simulation controller] Job LHS-000094 started. 55 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:19 KST [Local batch simulation controller] Job LHS-000095 started. 54 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:23 KST [Local batch simulation controller] Job LHS-000096 started. 53 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:23 KST [Local batch simulation controller] Job LHS-000097 started. 52 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:23 KST [Local batch simulation controller] Job LHS-000098 started. 51 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:26 KST [Local batch simulation controller] Job LHS-000099 started. 50 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:27 KST [Local batch simulation controller] Job LHS-000100 started. 49 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:27 KST [Local batch simulation controller] Job LHS-000101 started. 48 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:28 KST [Local batch simulation controller] Job LHS-000102 started. 47 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:31 KST [Local batch simulation controller] Job LHS-000103 started. 46 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:31 KST [Local batch simulation controller] Job LHS-000104 started. 45 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:32 KST [Local batch simulation controller] Job LHS-000105 started. 44 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:32 KST [Local batch simulation controller] Job LHS-000106 started. 43 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:36 KST [Local batch simulation controller] Job LHS-000107 started. 42 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:46 KST [Local batch simulation controller] Job LHS-000108 started. 41 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:46 KST [Local batch simulation controller] Job LHS-000109 started. 40 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:49 KST [Local batch simulation controller] Job LHS-000110 started. 39 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:34:56 KST [Local batch simulation controller] Job LHS-000111 started. 38 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:12 KST [Local batch simulation controller] Job LHS-000112 started. 37 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:38 KST [Local batch simulation controller] Job LHS-000113 started. 36 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:45 KST [Local batch simulation controller] Job LHS-000114 started. 35 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:52 KST [Local batch simulation controller] Job LHS-000115 started. 34 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:52 KST [Local batch simulation controller] Job LHS-000116 started. 33 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:54 KST [Local batch simulation controller] Job LHS-000117 started. 32 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:59 KST [Local batch simulation controller] Job LHS-000118 started. 31 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:35:59 KST [Local batch simulation controller] Job LHS-000119 started. 30 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:00 KST [Local batch simulation controller] Job LHS-000120 started. 29 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:05 KST [Local batch simulation controller] Job LHS-000121 started. 28 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:07 KST [Local batch simulation controller] Job LHS-000122 started. 27 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:07 KST [Local batch simulation controller] Job LHS-000123 started. 26 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:08 KST [Local batch simulation controller] Job LHS-000124 started. 25 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:10 KST [Local batch simulation controller] Job LHS-000125 started. 24 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:13 KST [Local batch simulation controller] Job LHS-000126 started. 23 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:15 KST [Local batch simulation controller] Job LHS-000127 started. 22 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:17 KST [Local batch simulation controller] Job LHS-000128 started. 21 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:21 KST [Local batch simulation controller] Job LHS-000129 started. 20 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:21 KST [Local batch simulation controller] Job LHS-000130 started. 19 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:21 KST [Local batch simulation controller] Job LHS-000131 started. 18 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:25 KST [Local batch simulation controller] Job LHS-000132 started. 17 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:30 KST [Local batch simulation controller] Job LHS-000133 started. 16 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:32 KST [Local batch simulation controller] Job LHS-000134 started. 15 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:34 KST [Local batch simulation controller] Job LHS-000135 started. 14 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:42 KST [Local batch simulation controller] Job LHS-000136 started. 13 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:42 KST [Local batch simulation controller] Job LHS-000137 started. 12 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:56 KST [Local batch simulation controller] Job LHS-000138 started. 11 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:36:57 KST [Local batch simulation controller] Job LHS-000139 started. 10 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:05 KST [Local batch simulation controller] Job LHS-000140 started. 9 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:11 KST [Local batch simulation controller] Job LHS-000141 started. 8 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:33 KST [Local batch simulation controller] Job LHS-000142 started. 7 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:42 KST [Local batch simulation controller] Job LHS-000143 started. 6 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:46 KST [Local batch simulation controller] Job LHS-000144 started. 5 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:48 KST [Local batch simulation controller] Job LHS-000145 started. 4 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:50 KST [Local batch simulation controller] Job LHS-000146 started. 3 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:51 KST [Local batch simulation controller] Job LHS-000147 started. 2 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:37:59 KST [Local batch simulation controller] Job LHS-000148 started. 1 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:38:02 KST [Local batch simulation controller] Job LHS-000149 started. 0 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:38:02 KST [Local batch simulation controller] Nearly there ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:08 KST [Local batch simulation controller] Local batch simulation controller is FINISHED [Que=0, Run=0, Fin=150]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Jul 2026 19:39:08 KST [Local batch simulation controller] Local agent stopped. </t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:08 KST [Local batch simulation controller] Collecting results ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:08 KST [Local batch simulation controller] Standard report collector collected 150 simulation reports in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\8\RunTimes.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:08 KST [Local batch simulation controller] Standard report collector collected job index table in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\8\SimJobIndex.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:10 KST [Local batch simulation controller] Combined result table AllCombinedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:10 KST [Local batch simulation controller] Derivative result table AllDerivedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:10 KST [Local batch simulation controller] All done!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:10 KST [Local batch simulation controller] Simulation finished at: Mon, 6 Jul 2026 19:39:10</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:39:10 KST [Local batch simulation controller] Total execution time = 621 seconds.</t>
+  </si>
+  <si>
+    <t>Simulation work directories and results will be stored in: D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\9\</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:02 KST [Local batch simulation controller] Writing job lists to D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\joblist_out.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:02 KST [Local batch simulation controller] Job LHS-000000 started. 149 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:03 KST [Local batch simulation controller] Job LHS-000001 started. 148 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000002 started. 147 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000003 started. 146 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000004 started. 145 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000005 started. 144 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000006 started. 143 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000007 started. 142 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000008 started. 141 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000009 started. 140 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:04 KST [Local batch simulation controller] Job LHS-000010 started. 139 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000011 started. 138 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000012 started. 137 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000013 started. 136 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000014 started. 135 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000015 started. 134 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000016 started. 133 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000017 started. 132 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000018 started. 131 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000019 started. 130 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:05 KST [Local batch simulation controller] Job LHS-000020 started. 129 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000021 started. 128 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000022 started. 127 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000023 started. 126 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000024 started. 125 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000025 started. 124 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000026 started. 123 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:40:06 KST [Local batch simulation controller] Job LHS-000027 started. 122 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:40 KST [Local batch simulation controller] Job LHS-000028 started. 121 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:43 KST [Local batch simulation controller] Job LHS-000029 started. 120 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:47 KST [Local batch simulation controller] Job LHS-000030 started. 119 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:50 KST [Local batch simulation controller] Job LHS-000031 started. 118 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:51 KST [Local batch simulation controller] Job LHS-000032 started. 117 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:52 KST [Local batch simulation controller] Job LHS-000033 started. 116 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:53 KST [Local batch simulation controller] Job LHS-000034 started. 115 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:54 KST [Local batch simulation controller] Job LHS-000035 started. 114 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:55 KST [Local batch simulation controller] Job LHS-000036 started. 113 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:55 KST [Local batch simulation controller] Job LHS-000037 started. 112 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:56 KST [Local batch simulation controller] Job LHS-000038 started. 111 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:57 KST [Local batch simulation controller] Job LHS-000039 started. 110 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:57 KST [Local batch simulation controller] Job LHS-000040 started. 109 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:59 KST [Local batch simulation controller] Job LHS-000041 started. 108 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:59 KST [Local batch simulation controller] Job LHS-000042 started. 107 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:59 KST [Local batch simulation controller] Job LHS-000043 started. 106 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:59 KST [Local batch simulation controller] Job LHS-000044 started. 105 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:41:59 KST [Local batch simulation controller] Job LHS-000045 started. 104 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:02 KST [Local batch simulation controller] Job LHS-000046 started. 103 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:03 KST [Local batch simulation controller] Job LHS-000047 started. 102 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:03 KST [Local batch simulation controller] Job LHS-000048 started. 101 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:06 KST [Local batch simulation controller] Job LHS-000049 started. 100 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:07 KST [Local batch simulation controller] Job LHS-000050 started. 99 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:08 KST [Local batch simulation controller] Job LHS-000051 started. 98 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:09 KST [Local batch simulation controller] Job LHS-000052 started. 97 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:13 KST [Local batch simulation controller] Job LHS-000053 started. 96 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:14 KST [Local batch simulation controller] Job LHS-000054 started. 95 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:42:17 KST [Local batch simulation controller] Job LHS-000055 started. 94 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:24 KST [Local batch simulation controller] Job LHS-000056 started. 93 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:30 KST [Local batch simulation controller] Job LHS-000057 started. 92 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:31 KST [Local batch simulation controller] Job LHS-000058 started. 91 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:36 KST [Local batch simulation controller] Job LHS-000059 started. 90 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:41 KST [Local batch simulation controller] Job LHS-000060 started. 89 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:41 KST [Local batch simulation controller] Job LHS-000061 started. 88 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:43 KST [Local batch simulation controller] Job LHS-000062 started. 87 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:43 KST [Local batch simulation controller] Job LHS-000063 started. 86 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:45 KST [Local batch simulation controller] Job LHS-000064 started. 85 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:47 KST [Local batch simulation controller] Job LHS-000065 started. 84 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:51 KST [Local batch simulation controller] Job LHS-000066 started. 83 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:51 KST [Local batch simulation controller] Job LHS-000067 started. 82 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:52 KST [Local batch simulation controller] Job LHS-000068 started. 81 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:53 KST [Local batch simulation controller] Job LHS-000069 started. 80 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:54 KST [Local batch simulation controller] Job LHS-000070 started. 79 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:54 KST [Local batch simulation controller] Job LHS-000071 started. 78 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:57 KST [Local batch simulation controller] Job LHS-000072 started. 77 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:58 KST [Local batch simulation controller] Job LHS-000073 started. 76 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:58 KST [Local batch simulation controller] Job LHS-000074 started. 75 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:58 KST [Local batch simulation controller] Job LHS-000075 started. 74 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:43:59 KST [Local batch simulation controller] Job LHS-000076 started. 73 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:00 KST [Local batch simulation controller] Job LHS-000077 started. 72 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:02 KST [Local batch simulation controller] Job LHS-000078 started. 71 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:03 KST [Local batch simulation controller] Job LHS-000079 started. 70 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:04 KST [Local batch simulation controller] Job LHS-000080 started. 69 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:07 KST [Local batch simulation controller] Job LHS-000081 started. 68 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:11 KST [Local batch simulation controller] Job LHS-000082 started. 67 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:44:15 KST [Local batch simulation controller] Job LHS-000083 started. 66 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:12 KST [Local batch simulation controller] Job LHS-000084 started. 65 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:19 KST [Local batch simulation controller] Job LHS-000085 started. 64 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:25 KST [Local batch simulation controller] Job LHS-000086 started. 63 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:27 KST [Local batch simulation controller] Job LHS-000087 started. 62 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:30 KST [Local batch simulation controller] Job LHS-000088 started. 61 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:30 KST [Local batch simulation controller] Job LHS-000089 started. 60 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:34 KST [Local batch simulation controller] Job LHS-000090 started. 59 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:36 KST [Local batch simulation controller] Job LHS-000091 started. 58 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:37 KST [Local batch simulation controller] Job LHS-000092 started. 57 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:40 KST [Local batch simulation controller] Job LHS-000093 started. 56 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:42 KST [Local batch simulation controller] Job LHS-000094 started. 55 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:45 KST [Local batch simulation controller] Job LHS-000095 started. 54 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:45 KST [Local batch simulation controller] Job LHS-000096 started. 53 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:47 KST [Local batch simulation controller] Job LHS-000097 started. 52 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:51 KST [Local batch simulation controller] Job LHS-000098 started. 51 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:52 KST [Local batch simulation controller] Job LHS-000099 started. 50 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:52 KST [Local batch simulation controller] Job LHS-000100 started. 49 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:54 KST [Local batch simulation controller] Job LHS-000101 started. 48 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:57 KST [Local batch simulation controller] Job LHS-000102 started. 47 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:58 KST [Local batch simulation controller] Job LHS-000103 started. 46 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:58 KST [Local batch simulation controller] Job LHS-000104 started. 45 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:58 KST [Local batch simulation controller] Job LHS-000105 started. 44 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:45:58 KST [Local batch simulation controller] Job LHS-000106 started. 43 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:46:10 KST [Local batch simulation controller] Job LHS-000107 started. 42 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:46:13 KST [Local batch simulation controller] Job LHS-000108 started. 41 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:46:14 KST [Local batch simulation controller] Job LHS-000109 started. 40 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:46:15 KST [Local batch simulation controller] Job LHS-000110 started. 39 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:46:21 KST [Local batch simulation controller] Job LHS-000111 started. 38 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:46:55 KST [Local batch simulation controller] Job LHS-000112 started. 37 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:17 KST [Local batch simulation controller] Job LHS-000113 started. 36 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:18 KST [Local batch simulation controller] Job LHS-000114 started. 35 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:20 KST [Local batch simulation controller] Job LHS-000115 started. 34 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:24 KST [Local batch simulation controller] Job LHS-000116 started. 33 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:25 KST [Local batch simulation controller] Job LHS-000117 started. 32 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:30 KST [Local batch simulation controller] Job LHS-000118 started. 31 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:31 KST [Local batch simulation controller] Job LHS-000119 started. 30 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:32 KST [Local batch simulation controller] Job LHS-000120 started. 29 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:34 KST [Local batch simulation controller] Job LHS-000121 started. 28 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:37 KST [Local batch simulation controller] Job LHS-000122 started. 27 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:39 KST [Local batch simulation controller] Job LHS-000123 started. 26 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:41 KST [Local batch simulation controller] Job LHS-000124 started. 25 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:41 KST [Local batch simulation controller] Job LHS-000125 started. 24 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:44 KST [Local batch simulation controller] Job LHS-000126 started. 23 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:46 KST [Local batch simulation controller] Job LHS-000127 started. 22 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:46 KST [Local batch simulation controller] Job LHS-000128 started. 21 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:46 KST [Local batch simulation controller] Job LHS-000129 started. 20 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:47 KST [Local batch simulation controller] Job LHS-000130 started. 19 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:48 KST [Local batch simulation controller] Job LHS-000131 started. 18 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:51 KST [Local batch simulation controller] Job LHS-000132 started. 17 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:47:51 KST [Local batch simulation controller] Job LHS-000133 started. 16 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:48:04 KST [Local batch simulation controller] Job LHS-000134 started. 15 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:48:04 KST [Local batch simulation controller] Job LHS-000135 started. 14 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:48:10 KST [Local batch simulation controller] Job LHS-000136 started. 13 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:48:12 KST [Local batch simulation controller] Job LHS-000137 started. 12 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:48:18 KST [Local batch simulation controller] Job LHS-000138 started. 11 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:48:21 KST [Local batch simulation controller] Job LHS-000139 started. 10 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:02 KST [Local batch simulation controller] Job LHS-000140 started. 9 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:03 KST [Local batch simulation controller] Job LHS-000141 started. 8 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:05 KST [Local batch simulation controller] Job LHS-000142 started. 7 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:09 KST [Local batch simulation controller] Job LHS-000143 started. 6 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:18 KST [Local batch simulation controller] Job LHS-000144 started. 5 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:22 KST [Local batch simulation controller] Job LHS-000145 started. 4 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:25 KST [Local batch simulation controller] Job LHS-000146 started. 3 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:29 KST [Local batch simulation controller] Job LHS-000147 started. 2 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:31 KST [Local batch simulation controller] Job LHS-000148 started. 1 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:36 KST [Local batch simulation controller] Job LHS-000149 started. 0 more to go!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:49:36 KST [Local batch simulation controller] Nearly there ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:39 KST [Local batch simulation controller] Local batch simulation controller is FINISHED [Que=0, Run=0, Fin=150]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Jul 2026 19:50:39 KST [Local batch simulation controller] Local agent stopped. </t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:39 KST [Local batch simulation controller] Collecting results ...</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:39 KST [Local batch simulation controller] Standard report collector collected 150 simulation reports in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\9\RunTimes.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:39 KST [Local batch simulation controller] Standard report collector collected job index table in D:\1. Research\0. CONFERENCE PAPER\2026.09_ICAE2026\3. DATA_CODE\CODE\data\jEPlus-LHS\0_Test\0_LHS external test\9\SimJobIndex.csv</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:41 KST [Local batch simulation controller] Combined result table AllCombinedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:41 KST [Local batch simulation controller] Derivative result table AllDerivedResults.csv is created.</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:41 KST [Local batch simulation controller] All done!</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:41 KST [Local batch simulation controller] Simulation finished at: Mon, 6 Jul 2026 19:50:41</t>
+  </si>
+  <si>
+    <t>6 Jul 2026 19:50:41 KST [Local batch simulation controller] Total execution time = 638 seconds.</t>
   </si>
 </sst>
 </file>
@@ -11808,7 +14742,7 @@
       <charset val="163"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -11833,6 +14767,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -11864,7 +14804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -11919,6 +14859,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -29546,71 +32487,105 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E8C98C-B162-4183-BB44-6FD0550950F1}">
-  <dimension ref="A1:B563"/>
+  <dimension ref="A1:D1637"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>3573</v>
       </c>
       <c r="B1" s="25"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>3081</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D2" s="23" t="s">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>687</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>690</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>695</v>
       </c>
@@ -32268,6 +35243,5237 @@
     <row r="563" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>3572</v>
+      </c>
+    </row>
+    <row r="565" spans="1:1" s="26" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A566" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A567" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A568" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A569" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A570" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A571" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A573" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A574" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A575" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A577" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A579" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A580" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A581" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A582" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A583" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A585" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A586" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A587" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A589" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A591" t="s">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A592" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A593" t="s">
+        <v>3575</v>
+      </c>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A594" t="s">
+        <v>3576</v>
+      </c>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A595" t="s">
+        <v>3577</v>
+      </c>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A596" t="s">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A597" t="s">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A598" t="s">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A599" t="s">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A600" t="s">
+        <v>3582</v>
+      </c>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A601" t="s">
+        <v>3583</v>
+      </c>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A602" t="s">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A603" t="s">
+        <v>3585</v>
+      </c>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A604" t="s">
+        <v>3586</v>
+      </c>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A605" t="s">
+        <v>3587</v>
+      </c>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A606" t="s">
+        <v>3588</v>
+      </c>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A607" t="s">
+        <v>3589</v>
+      </c>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A608" t="s">
+        <v>3590</v>
+      </c>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A609" t="s">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A610" t="s">
+        <v>3592</v>
+      </c>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A611" t="s">
+        <v>3593</v>
+      </c>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A612" t="s">
+        <v>3594</v>
+      </c>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A613" t="s">
+        <v>3595</v>
+      </c>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A614" t="s">
+        <v>3596</v>
+      </c>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A615" t="s">
+        <v>3597</v>
+      </c>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A616" t="s">
+        <v>3598</v>
+      </c>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A617" t="s">
+        <v>3599</v>
+      </c>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A618" t="s">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A619" t="s">
+        <v>3601</v>
+      </c>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A620" t="s">
+        <v>3602</v>
+      </c>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A621" t="s">
+        <v>3603</v>
+      </c>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A622" t="s">
+        <v>3604</v>
+      </c>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A623" t="s">
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A624" t="s">
+        <v>3606</v>
+      </c>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A625" t="s">
+        <v>3607</v>
+      </c>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A626" t="s">
+        <v>3608</v>
+      </c>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A627" t="s">
+        <v>3609</v>
+      </c>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A628" t="s">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A629" t="s">
+        <v>3611</v>
+      </c>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A630" t="s">
+        <v>3612</v>
+      </c>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A631" t="s">
+        <v>3613</v>
+      </c>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A632" t="s">
+        <v>3614</v>
+      </c>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A633" t="s">
+        <v>3615</v>
+      </c>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A634" t="s">
+        <v>3616</v>
+      </c>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A635" t="s">
+        <v>3617</v>
+      </c>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A636" t="s">
+        <v>3618</v>
+      </c>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A637" t="s">
+        <v>3619</v>
+      </c>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A638" t="s">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A639" t="s">
+        <v>3621</v>
+      </c>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A640" t="s">
+        <v>3622</v>
+      </c>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A641" t="s">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A642" t="s">
+        <v>3624</v>
+      </c>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A643" t="s">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A644" t="s">
+        <v>3626</v>
+      </c>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A645" t="s">
+        <v>3627</v>
+      </c>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A646" t="s">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A647" t="s">
+        <v>3629</v>
+      </c>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A648" t="s">
+        <v>3630</v>
+      </c>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A649" t="s">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A650" t="s">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A651" t="s">
+        <v>3633</v>
+      </c>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A652" t="s">
+        <v>3634</v>
+      </c>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A653" t="s">
+        <v>3635</v>
+      </c>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A654" t="s">
+        <v>3636</v>
+      </c>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A655" t="s">
+        <v>3637</v>
+      </c>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A656" t="s">
+        <v>3638</v>
+      </c>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A657" t="s">
+        <v>3639</v>
+      </c>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A658" t="s">
+        <v>3640</v>
+      </c>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A659" t="s">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A660" t="s">
+        <v>3642</v>
+      </c>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A661" t="s">
+        <v>3643</v>
+      </c>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A662" t="s">
+        <v>3644</v>
+      </c>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A663" t="s">
+        <v>3645</v>
+      </c>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A664" t="s">
+        <v>3646</v>
+      </c>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A665" t="s">
+        <v>3647</v>
+      </c>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A666" t="s">
+        <v>3648</v>
+      </c>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A667" t="s">
+        <v>3649</v>
+      </c>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A668" t="s">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A669" t="s">
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A670" t="s">
+        <v>3652</v>
+      </c>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A671" t="s">
+        <v>3653</v>
+      </c>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A672" t="s">
+        <v>3654</v>
+      </c>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A673" t="s">
+        <v>3655</v>
+      </c>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A674" t="s">
+        <v>3656</v>
+      </c>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A675" t="s">
+        <v>3657</v>
+      </c>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A676" t="s">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A677" t="s">
+        <v>3659</v>
+      </c>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A678" t="s">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A679" t="s">
+        <v>3661</v>
+      </c>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A680" t="s">
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A681" t="s">
+        <v>3663</v>
+      </c>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A682" t="s">
+        <v>3664</v>
+      </c>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A683" t="s">
+        <v>3665</v>
+      </c>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A684" t="s">
+        <v>3666</v>
+      </c>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A685" t="s">
+        <v>3667</v>
+      </c>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A686" t="s">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A687" t="s">
+        <v>3669</v>
+      </c>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A688" t="s">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A689" t="s">
+        <v>3671</v>
+      </c>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A690" t="s">
+        <v>3672</v>
+      </c>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A691" t="s">
+        <v>3673</v>
+      </c>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A692" t="s">
+        <v>3674</v>
+      </c>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A693" t="s">
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A694" t="s">
+        <v>3676</v>
+      </c>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A695" t="s">
+        <v>3677</v>
+      </c>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A696" t="s">
+        <v>3678</v>
+      </c>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A697" t="s">
+        <v>3679</v>
+      </c>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A698" t="s">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A699" t="s">
+        <v>3681</v>
+      </c>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A700" t="s">
+        <v>3682</v>
+      </c>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A701" t="s">
+        <v>3683</v>
+      </c>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A702" t="s">
+        <v>3684</v>
+      </c>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A703" t="s">
+        <v>3685</v>
+      </c>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A704" t="s">
+        <v>3686</v>
+      </c>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A705" t="s">
+        <v>3687</v>
+      </c>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A706" t="s">
+        <v>3688</v>
+      </c>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A707" t="s">
+        <v>3689</v>
+      </c>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A708" t="s">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A709" t="s">
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A710" t="s">
+        <v>3692</v>
+      </c>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A711" t="s">
+        <v>3693</v>
+      </c>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A712" t="s">
+        <v>3694</v>
+      </c>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A713" t="s">
+        <v>3695</v>
+      </c>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A714" t="s">
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A715" t="s">
+        <v>3697</v>
+      </c>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A716" t="s">
+        <v>3698</v>
+      </c>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A717" t="s">
+        <v>3699</v>
+      </c>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A718" t="s">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A719" t="s">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A720" t="s">
+        <v>3702</v>
+      </c>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A721" t="s">
+        <v>3703</v>
+      </c>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A722" t="s">
+        <v>3704</v>
+      </c>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A723" t="s">
+        <v>3705</v>
+      </c>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A724" t="s">
+        <v>3706</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A725" t="s">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A726" t="s">
+        <v>3708</v>
+      </c>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A727" t="s">
+        <v>3709</v>
+      </c>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A728" t="s">
+        <v>3710</v>
+      </c>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A729" t="s">
+        <v>3711</v>
+      </c>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A730" t="s">
+        <v>3712</v>
+      </c>
+    </row>
+    <row r="731" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A731" t="s">
+        <v>3713</v>
+      </c>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A732" t="s">
+        <v>3714</v>
+      </c>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A733" t="s">
+        <v>3715</v>
+      </c>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A734" t="s">
+        <v>3716</v>
+      </c>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A735" t="s">
+        <v>3717</v>
+      </c>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A736" t="s">
+        <v>3718</v>
+      </c>
+    </row>
+    <row r="737" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A737" t="s">
+        <v>3719</v>
+      </c>
+    </row>
+    <row r="738" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A738" t="s">
+        <v>3720</v>
+      </c>
+    </row>
+    <row r="739" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A739" t="s">
+        <v>3721</v>
+      </c>
+    </row>
+    <row r="740" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A740" t="s">
+        <v>3722</v>
+      </c>
+    </row>
+    <row r="741" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A741" t="s">
+        <v>3723</v>
+      </c>
+    </row>
+    <row r="742" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A742" t="s">
+        <v>3724</v>
+      </c>
+    </row>
+    <row r="743" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A743" t="s">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="744" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A744" t="s">
+        <v>3726</v>
+      </c>
+    </row>
+    <row r="745" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A745" t="s">
+        <v>3727</v>
+      </c>
+    </row>
+    <row r="746" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A746" t="s">
+        <v>3728</v>
+      </c>
+    </row>
+    <row r="747" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A747" t="s">
+        <v>3729</v>
+      </c>
+    </row>
+    <row r="748" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A748" t="s">
+        <v>3730</v>
+      </c>
+    </row>
+    <row r="749" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A749" t="s">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="750" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A750" t="s">
+        <v>3732</v>
+      </c>
+    </row>
+    <row r="751" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A751" t="s">
+        <v>3733</v>
+      </c>
+    </row>
+    <row r="752" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A752" t="s">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="753" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A753" t="s">
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="754" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A754" t="s">
+        <v>3736</v>
+      </c>
+    </row>
+    <row r="756" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A756" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="757" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A757" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="758" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A758" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="759" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A759" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="761" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A761" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="762" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A762" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="763" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A763" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="765" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A765" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="767" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A767" t="s">
+        <v>3737</v>
+      </c>
+    </row>
+    <row r="768" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A768" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="769" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A769" t="s">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="770" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A770" t="s">
+        <v>3739</v>
+      </c>
+    </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A771" t="s">
+        <v>3740</v>
+      </c>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A772" t="s">
+        <v>3741</v>
+      </c>
+    </row>
+    <row r="773" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A773" t="s">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A774" t="s">
+        <v>3743</v>
+      </c>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A775" t="s">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A776" t="s">
+        <v>3745</v>
+      </c>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A777" t="s">
+        <v>3746</v>
+      </c>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A778" t="s">
+        <v>3747</v>
+      </c>
+    </row>
+    <row r="779" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A779" t="s">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A780" t="s">
+        <v>3749</v>
+      </c>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A781" t="s">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A782" t="s">
+        <v>3751</v>
+      </c>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A783" t="s">
+        <v>3752</v>
+      </c>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A784" t="s">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="785" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A785" t="s">
+        <v>3754</v>
+      </c>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A786" t="s">
+        <v>3755</v>
+      </c>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A787" t="s">
+        <v>3756</v>
+      </c>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A788" t="s">
+        <v>3757</v>
+      </c>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A789" t="s">
+        <v>3758</v>
+      </c>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A790" t="s">
+        <v>3759</v>
+      </c>
+    </row>
+    <row r="791" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A791" t="s">
+        <v>3760</v>
+      </c>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A792" t="s">
+        <v>3761</v>
+      </c>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A793" t="s">
+        <v>3762</v>
+      </c>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A794" t="s">
+        <v>3763</v>
+      </c>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A795" t="s">
+        <v>3764</v>
+      </c>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A796" t="s">
+        <v>3765</v>
+      </c>
+    </row>
+    <row r="797" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A797" t="s">
+        <v>3766</v>
+      </c>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A798" t="s">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A799" t="s">
+        <v>3768</v>
+      </c>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A800" t="s">
+        <v>3769</v>
+      </c>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A801" t="s">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A802" t="s">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="803" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A803" t="s">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A804" t="s">
+        <v>3773</v>
+      </c>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A805" t="s">
+        <v>3774</v>
+      </c>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A806" t="s">
+        <v>3775</v>
+      </c>
+    </row>
+    <row r="807" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A807" t="s">
+        <v>3776</v>
+      </c>
+    </row>
+    <row r="808" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A808" t="s">
+        <v>3777</v>
+      </c>
+    </row>
+    <row r="809" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A809" t="s">
+        <v>3778</v>
+      </c>
+    </row>
+    <row r="810" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A810" t="s">
+        <v>3779</v>
+      </c>
+    </row>
+    <row r="811" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A811" t="s">
+        <v>3780</v>
+      </c>
+    </row>
+    <row r="812" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A812" t="s">
+        <v>3781</v>
+      </c>
+    </row>
+    <row r="813" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A813" t="s">
+        <v>3782</v>
+      </c>
+    </row>
+    <row r="814" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A814" t="s">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="815" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A815" t="s">
+        <v>3784</v>
+      </c>
+    </row>
+    <row r="816" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A816" t="s">
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="817" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A817" t="s">
+        <v>3786</v>
+      </c>
+    </row>
+    <row r="818" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A818" t="s">
+        <v>3787</v>
+      </c>
+    </row>
+    <row r="819" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A819" t="s">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="820" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A820" t="s">
+        <v>3789</v>
+      </c>
+    </row>
+    <row r="821" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A821" t="s">
+        <v>3790</v>
+      </c>
+    </row>
+    <row r="822" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A822" t="s">
+        <v>3791</v>
+      </c>
+    </row>
+    <row r="823" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A823" t="s">
+        <v>3792</v>
+      </c>
+    </row>
+    <row r="824" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A824" t="s">
+        <v>3793</v>
+      </c>
+    </row>
+    <row r="825" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A825" t="s">
+        <v>3794</v>
+      </c>
+    </row>
+    <row r="826" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A826" t="s">
+        <v>3795</v>
+      </c>
+    </row>
+    <row r="827" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A827" t="s">
+        <v>3796</v>
+      </c>
+    </row>
+    <row r="828" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A828" t="s">
+        <v>3797</v>
+      </c>
+    </row>
+    <row r="829" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A829" t="s">
+        <v>3798</v>
+      </c>
+    </row>
+    <row r="830" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A830" t="s">
+        <v>3799</v>
+      </c>
+    </row>
+    <row r="831" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A831" t="s">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="832" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A832" t="s">
+        <v>3801</v>
+      </c>
+    </row>
+    <row r="833" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A833" t="s">
+        <v>3802</v>
+      </c>
+    </row>
+    <row r="834" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A834" t="s">
+        <v>3803</v>
+      </c>
+    </row>
+    <row r="835" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A835" t="s">
+        <v>3804</v>
+      </c>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A836" t="s">
+        <v>3805</v>
+      </c>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A837" t="s">
+        <v>3806</v>
+      </c>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A838" t="s">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="839" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A839" t="s">
+        <v>3808</v>
+      </c>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A840" t="s">
+        <v>3809</v>
+      </c>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A841" t="s">
+        <v>3810</v>
+      </c>
+    </row>
+    <row r="842" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A842" t="s">
+        <v>3811</v>
+      </c>
+    </row>
+    <row r="843" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A843" t="s">
+        <v>3812</v>
+      </c>
+    </row>
+    <row r="844" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A844" t="s">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="845" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A845" t="s">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="846" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A846" t="s">
+        <v>3815</v>
+      </c>
+    </row>
+    <row r="847" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A847" t="s">
+        <v>3816</v>
+      </c>
+    </row>
+    <row r="848" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A848" t="s">
+        <v>3817</v>
+      </c>
+    </row>
+    <row r="849" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A849" t="s">
+        <v>3818</v>
+      </c>
+    </row>
+    <row r="850" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A850" t="s">
+        <v>3819</v>
+      </c>
+    </row>
+    <row r="851" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A851" t="s">
+        <v>3820</v>
+      </c>
+    </row>
+    <row r="852" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A852" t="s">
+        <v>3821</v>
+      </c>
+    </row>
+    <row r="853" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A853" t="s">
+        <v>3822</v>
+      </c>
+    </row>
+    <row r="854" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A854" t="s">
+        <v>3823</v>
+      </c>
+    </row>
+    <row r="855" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A855" t="s">
+        <v>3824</v>
+      </c>
+    </row>
+    <row r="856" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A856" t="s">
+        <v>3825</v>
+      </c>
+    </row>
+    <row r="857" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A857" t="s">
+        <v>3826</v>
+      </c>
+    </row>
+    <row r="858" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A858" t="s">
+        <v>3827</v>
+      </c>
+    </row>
+    <row r="859" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A859" t="s">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="860" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A860" t="s">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="861" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A861" t="s">
+        <v>3830</v>
+      </c>
+    </row>
+    <row r="862" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A862" t="s">
+        <v>3831</v>
+      </c>
+    </row>
+    <row r="863" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A863" t="s">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="864" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A864" t="s">
+        <v>3833</v>
+      </c>
+    </row>
+    <row r="865" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A865" t="s">
+        <v>3834</v>
+      </c>
+    </row>
+    <row r="866" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A866" t="s">
+        <v>3835</v>
+      </c>
+    </row>
+    <row r="867" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A867" t="s">
+        <v>3836</v>
+      </c>
+    </row>
+    <row r="868" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A868" t="s">
+        <v>3837</v>
+      </c>
+    </row>
+    <row r="869" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A869" t="s">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="870" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A870" t="s">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="871" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A871" t="s">
+        <v>3840</v>
+      </c>
+    </row>
+    <row r="872" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A872" t="s">
+        <v>3841</v>
+      </c>
+    </row>
+    <row r="873" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A873" t="s">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="874" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A874" t="s">
+        <v>3843</v>
+      </c>
+    </row>
+    <row r="875" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A875" t="s">
+        <v>3844</v>
+      </c>
+    </row>
+    <row r="876" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A876" t="s">
+        <v>3845</v>
+      </c>
+    </row>
+    <row r="877" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A877" t="s">
+        <v>3846</v>
+      </c>
+    </row>
+    <row r="878" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A878" t="s">
+        <v>3847</v>
+      </c>
+    </row>
+    <row r="879" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A879" t="s">
+        <v>3848</v>
+      </c>
+    </row>
+    <row r="880" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A880" t="s">
+        <v>3849</v>
+      </c>
+    </row>
+    <row r="881" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A881" t="s">
+        <v>3850</v>
+      </c>
+    </row>
+    <row r="882" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A882" t="s">
+        <v>3851</v>
+      </c>
+    </row>
+    <row r="883" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A883" t="s">
+        <v>3852</v>
+      </c>
+    </row>
+    <row r="884" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A884" t="s">
+        <v>3853</v>
+      </c>
+    </row>
+    <row r="885" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A885" t="s">
+        <v>3854</v>
+      </c>
+    </row>
+    <row r="886" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A886" t="s">
+        <v>3855</v>
+      </c>
+    </row>
+    <row r="887" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A887" t="s">
+        <v>3856</v>
+      </c>
+    </row>
+    <row r="888" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A888" t="s">
+        <v>3857</v>
+      </c>
+    </row>
+    <row r="889" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A889" t="s">
+        <v>3858</v>
+      </c>
+    </row>
+    <row r="890" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A890" t="s">
+        <v>3859</v>
+      </c>
+    </row>
+    <row r="891" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A891" t="s">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="892" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A892" t="s">
+        <v>3861</v>
+      </c>
+    </row>
+    <row r="893" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A893" t="s">
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="894" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A894" t="s">
+        <v>3863</v>
+      </c>
+    </row>
+    <row r="895" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A895" t="s">
+        <v>3864</v>
+      </c>
+    </row>
+    <row r="896" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A896" t="s">
+        <v>3865</v>
+      </c>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A897" t="s">
+        <v>3866</v>
+      </c>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A898" t="s">
+        <v>3867</v>
+      </c>
+    </row>
+    <row r="899" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A899" t="s">
+        <v>3868</v>
+      </c>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A900" t="s">
+        <v>3869</v>
+      </c>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A901" t="s">
+        <v>3870</v>
+      </c>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A902" t="s">
+        <v>3871</v>
+      </c>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A903" t="s">
+        <v>3872</v>
+      </c>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A904" t="s">
+        <v>3873</v>
+      </c>
+    </row>
+    <row r="905" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A905" t="s">
+        <v>3874</v>
+      </c>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A906" t="s">
+        <v>3875</v>
+      </c>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A907" t="s">
+        <v>3876</v>
+      </c>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A908" t="s">
+        <v>3877</v>
+      </c>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A909" t="s">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A910" t="s">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="911" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A911" t="s">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A912" t="s">
+        <v>3881</v>
+      </c>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A913" t="s">
+        <v>3882</v>
+      </c>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A914" t="s">
+        <v>3883</v>
+      </c>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A915" t="s">
+        <v>3884</v>
+      </c>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A916" t="s">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="917" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A917" t="s">
+        <v>3886</v>
+      </c>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A918" t="s">
+        <v>3887</v>
+      </c>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A919" t="s">
+        <v>3888</v>
+      </c>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A920" t="s">
+        <v>3889</v>
+      </c>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A921" t="s">
+        <v>3890</v>
+      </c>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A922" t="s">
+        <v>3891</v>
+      </c>
+    </row>
+    <row r="923" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A923" t="s">
+        <v>3892</v>
+      </c>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A924" t="s">
+        <v>3893</v>
+      </c>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A925" t="s">
+        <v>3894</v>
+      </c>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A926" t="s">
+        <v>3895</v>
+      </c>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A927" t="s">
+        <v>3896</v>
+      </c>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A928" t="s">
+        <v>3897</v>
+      </c>
+    </row>
+    <row r="929" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A929" t="s">
+        <v>3898</v>
+      </c>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A930" t="s">
+        <v>3899</v>
+      </c>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A932" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A933" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A934" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="935" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A935" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A936" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A937" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A938" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A940" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="941" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A941" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A942" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A944" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A946" t="s">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="947" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A947" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A948" t="s">
+        <v>3901</v>
+      </c>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A949" t="s">
+        <v>3902</v>
+      </c>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A950" t="s">
+        <v>3903</v>
+      </c>
+    </row>
+    <row r="951" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A951" t="s">
+        <v>3904</v>
+      </c>
+    </row>
+    <row r="952" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A952" t="s">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="953" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A953" t="s">
+        <v>3906</v>
+      </c>
+    </row>
+    <row r="954" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A954" t="s">
+        <v>3907</v>
+      </c>
+    </row>
+    <row r="955" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A955" t="s">
+        <v>3908</v>
+      </c>
+    </row>
+    <row r="956" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A956" t="s">
+        <v>3909</v>
+      </c>
+    </row>
+    <row r="957" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A957" t="s">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="958" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A958" t="s">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="959" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A959" t="s">
+        <v>3912</v>
+      </c>
+    </row>
+    <row r="960" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A960" t="s">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="961" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A961" t="s">
+        <v>3914</v>
+      </c>
+    </row>
+    <row r="962" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A962" t="s">
+        <v>3915</v>
+      </c>
+    </row>
+    <row r="963" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A963" t="s">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="964" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A964" t="s">
+        <v>3917</v>
+      </c>
+    </row>
+    <row r="965" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A965" t="s">
+        <v>3918</v>
+      </c>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A966" t="s">
+        <v>3919</v>
+      </c>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A967" t="s">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A968" t="s">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="969" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A969" t="s">
+        <v>3922</v>
+      </c>
+    </row>
+    <row r="970" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A970" t="s">
+        <v>3923</v>
+      </c>
+    </row>
+    <row r="971" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A971" t="s">
+        <v>3924</v>
+      </c>
+    </row>
+    <row r="972" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A972" t="s">
+        <v>3925</v>
+      </c>
+    </row>
+    <row r="973" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A973" t="s">
+        <v>3926</v>
+      </c>
+    </row>
+    <row r="974" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A974" t="s">
+        <v>3927</v>
+      </c>
+    </row>
+    <row r="975" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A975" t="s">
+        <v>3928</v>
+      </c>
+    </row>
+    <row r="976" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A976" t="s">
+        <v>3929</v>
+      </c>
+    </row>
+    <row r="977" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A977" t="s">
+        <v>3930</v>
+      </c>
+    </row>
+    <row r="978" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A978" t="s">
+        <v>3931</v>
+      </c>
+    </row>
+    <row r="979" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A979" t="s">
+        <v>3932</v>
+      </c>
+    </row>
+    <row r="980" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A980" t="s">
+        <v>3933</v>
+      </c>
+    </row>
+    <row r="981" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A981" t="s">
+        <v>3934</v>
+      </c>
+    </row>
+    <row r="982" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A982" t="s">
+        <v>3935</v>
+      </c>
+    </row>
+    <row r="983" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A983" t="s">
+        <v>3936</v>
+      </c>
+    </row>
+    <row r="984" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A984" t="s">
+        <v>3937</v>
+      </c>
+    </row>
+    <row r="985" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A985" t="s">
+        <v>3938</v>
+      </c>
+    </row>
+    <row r="986" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A986" t="s">
+        <v>3939</v>
+      </c>
+    </row>
+    <row r="987" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A987" t="s">
+        <v>3940</v>
+      </c>
+    </row>
+    <row r="988" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A988" t="s">
+        <v>3941</v>
+      </c>
+    </row>
+    <row r="989" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A989" t="s">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="990" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A990" t="s">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="991" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A991" t="s">
+        <v>3944</v>
+      </c>
+    </row>
+    <row r="992" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A992" t="s">
+        <v>3945</v>
+      </c>
+    </row>
+    <row r="993" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A993" t="s">
+        <v>3946</v>
+      </c>
+    </row>
+    <row r="994" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A994" t="s">
+        <v>3947</v>
+      </c>
+    </row>
+    <row r="995" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A995" t="s">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="996" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A996" t="s">
+        <v>3949</v>
+      </c>
+    </row>
+    <row r="997" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A997" t="s">
+        <v>3950</v>
+      </c>
+    </row>
+    <row r="998" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A998" t="s">
+        <v>3951</v>
+      </c>
+    </row>
+    <row r="999" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A999" t="s">
+        <v>3952</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1000" t="s">
+        <v>3953</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1001" t="s">
+        <v>3954</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1002" t="s">
+        <v>3955</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1003" t="s">
+        <v>3956</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1004" t="s">
+        <v>3957</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1005" t="s">
+        <v>3958</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1006" t="s">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1007" t="s">
+        <v>3960</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1008" t="s">
+        <v>3961</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1009" t="s">
+        <v>3962</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1010" t="s">
+        <v>3963</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1011" t="s">
+        <v>3964</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1012" t="s">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1013" t="s">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1014" t="s">
+        <v>3967</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1015" t="s">
+        <v>3968</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1016" t="s">
+        <v>3969</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1017" t="s">
+        <v>3970</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1018" t="s">
+        <v>3971</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1019" t="s">
+        <v>3972</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1020" t="s">
+        <v>3973</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1021" t="s">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1022" t="s">
+        <v>3975</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1023" t="s">
+        <v>3976</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1024" t="s">
+        <v>3977</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1025" t="s">
+        <v>3978</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1026" t="s">
+        <v>3979</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1027" t="s">
+        <v>3980</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1028" t="s">
+        <v>3981</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1029" t="s">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1030" t="s">
+        <v>3983</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1031" t="s">
+        <v>3984</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1032" t="s">
+        <v>3985</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1033" t="s">
+        <v>3986</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1034" t="s">
+        <v>3987</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1035" t="s">
+        <v>3988</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1036" t="s">
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1037" t="s">
+        <v>3990</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1038" t="s">
+        <v>3991</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1039" t="s">
+        <v>3992</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1040" t="s">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1041" t="s">
+        <v>3994</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1042" t="s">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1043" t="s">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1044" t="s">
+        <v>3997</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1045" t="s">
+        <v>3998</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1046" t="s">
+        <v>3999</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1047" t="s">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1048" t="s">
+        <v>4001</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1049" t="s">
+        <v>4002</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1050" t="s">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1051" t="s">
+        <v>4004</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1052" t="s">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1053" t="s">
+        <v>4006</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1054" t="s">
+        <v>4007</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1055" t="s">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1056" t="s">
+        <v>4009</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1057" t="s">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1058" t="s">
+        <v>4011</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1059" t="s">
+        <v>4012</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1060" t="s">
+        <v>4013</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1061" t="s">
+        <v>4014</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1062" t="s">
+        <v>4015</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1063" t="s">
+        <v>4016</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1064" t="s">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1065" t="s">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1066" t="s">
+        <v>4019</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1067" t="s">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1068" t="s">
+        <v>4021</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1069" t="s">
+        <v>4022</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1070" t="s">
+        <v>4023</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1071" t="s">
+        <v>4024</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1072" t="s">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1073" t="s">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1074" t="s">
+        <v>4027</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1075" t="s">
+        <v>4028</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1076" t="s">
+        <v>4029</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1077" t="s">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1078" t="s">
+        <v>4031</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1079" t="s">
+        <v>4032</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1080" t="s">
+        <v>4033</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1081" t="s">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1082" t="s">
+        <v>4035</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1083" t="s">
+        <v>4036</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1084" t="s">
+        <v>4037</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1085" t="s">
+        <v>4038</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1086" t="s">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1087" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1088" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1089" t="s">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1090" t="s">
+        <v>4043</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1091" t="s">
+        <v>4044</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1092" t="s">
+        <v>4045</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1093" t="s">
+        <v>4046</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1094" t="s">
+        <v>4047</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1095" t="s">
+        <v>4048</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1096" t="s">
+        <v>4049</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1097" t="s">
+        <v>4050</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1098" t="s">
+        <v>4051</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1099" t="s">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1100" t="s">
+        <v>4053</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1101" t="s">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1102" t="s">
+        <v>4055</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1103" t="s">
+        <v>4056</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1104" t="s">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1105" t="s">
+        <v>4058</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1106" t="s">
+        <v>4059</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1107" t="s">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1108" t="s">
+        <v>4061</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1109" t="s">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1111" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1112" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1113" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1114" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1116" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1117" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1118" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1120" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1122" t="s">
+        <v>4063</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1123" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1124" t="s">
+        <v>4064</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1125" t="s">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1126" t="s">
+        <v>4066</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1127" t="s">
+        <v>4067</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1128" t="s">
+        <v>4068</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1129" t="s">
+        <v>4069</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1130" t="s">
+        <v>4070</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1131" t="s">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1132" t="s">
+        <v>4072</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1133" t="s">
+        <v>4073</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1134" t="s">
+        <v>4074</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1135" t="s">
+        <v>4075</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1136" t="s">
+        <v>4076</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1137" t="s">
+        <v>4077</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1138" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1139" t="s">
+        <v>4079</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1140" t="s">
+        <v>4080</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1141" t="s">
+        <v>4081</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1142" t="s">
+        <v>4082</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1143" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1144" t="s">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1145" t="s">
+        <v>4085</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1146" t="s">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1147" t="s">
+        <v>4087</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1148" t="s">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1149" t="s">
+        <v>4089</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1150" t="s">
+        <v>4090</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1151" t="s">
+        <v>4091</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1152" t="s">
+        <v>4092</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1153" t="s">
+        <v>4093</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1154" t="s">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1155" t="s">
+        <v>4095</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1156" t="s">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1157" t="s">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1158" t="s">
+        <v>4098</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1159" t="s">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1160" t="s">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1161" t="s">
+        <v>4101</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1162" t="s">
+        <v>4102</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1163" t="s">
+        <v>4103</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1164" t="s">
+        <v>4104</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1165" t="s">
+        <v>4105</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1166" t="s">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1167" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1168" t="s">
+        <v>4108</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1169" t="s">
+        <v>4109</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1170" t="s">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1171" t="s">
+        <v>4111</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1172" t="s">
+        <v>4112</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1173" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1174" t="s">
+        <v>4114</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1175" t="s">
+        <v>4115</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1176" t="s">
+        <v>4116</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1177" t="s">
+        <v>4117</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1178" t="s">
+        <v>4118</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1179" t="s">
+        <v>4119</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1180" t="s">
+        <v>4120</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1181" t="s">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1182" t="s">
+        <v>4122</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1183" t="s">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1184" t="s">
+        <v>4124</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1185" t="s">
+        <v>4125</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1186" t="s">
+        <v>4126</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1187" t="s">
+        <v>4127</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1188" t="s">
+        <v>4128</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1189" t="s">
+        <v>4129</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1190" t="s">
+        <v>4130</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1191" t="s">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1192" t="s">
+        <v>4132</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1193" t="s">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1194" t="s">
+        <v>4134</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1195" t="s">
+        <v>4135</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1196" t="s">
+        <v>4136</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1197" t="s">
+        <v>4137</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1198" t="s">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1199" t="s">
+        <v>4139</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1200" t="s">
+        <v>4140</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1201" t="s">
+        <v>4141</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1202" t="s">
+        <v>4142</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1203" t="s">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1204" t="s">
+        <v>4144</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1205" t="s">
+        <v>4145</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1206" t="s">
+        <v>4146</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1207" t="s">
+        <v>4147</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1208" t="s">
+        <v>4148</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1209" t="s">
+        <v>4149</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1210" t="s">
+        <v>4150</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1211" t="s">
+        <v>4151</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1212" t="s">
+        <v>4152</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1213" t="s">
+        <v>4153</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1214" t="s">
+        <v>4154</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1215" t="s">
+        <v>4155</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1216" t="s">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1217" t="s">
+        <v>4157</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1218" t="s">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1219" t="s">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1220" t="s">
+        <v>4160</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1221" t="s">
+        <v>4161</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1222" t="s">
+        <v>4162</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1223" t="s">
+        <v>4163</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1224" t="s">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1225" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1226" t="s">
+        <v>4166</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1227" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1228" t="s">
+        <v>4168</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1229" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1230" t="s">
+        <v>4170</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1231" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1232" t="s">
+        <v>4172</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1233" t="s">
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1234" t="s">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1235" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1236" t="s">
+        <v>4176</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1237" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1238" t="s">
+        <v>4178</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1239" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1240" t="s">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1241" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1242" t="s">
+        <v>4182</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1243" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1244" t="s">
+        <v>4184</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1245" t="s">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1246" t="s">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1247" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1248" t="s">
+        <v>4188</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1249" t="s">
+        <v>4189</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1250" t="s">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1251" t="s">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1252" t="s">
+        <v>4192</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1253" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1254" t="s">
+        <v>4194</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1255" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1256" t="s">
+        <v>4196</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1257" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1258" t="s">
+        <v>4198</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1259" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1260" t="s">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1261" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1262" t="s">
+        <v>4202</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1263" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1264" t="s">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1265" t="s">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1266" t="s">
+        <v>4206</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1267" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1268" t="s">
+        <v>4208</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1269" t="s">
+        <v>4209</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1270" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1271" t="s">
+        <v>4211</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1272" t="s">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1273" t="s">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1274" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1275" t="s">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1276" t="s">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1277" t="s">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1278" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1279" t="s">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1280" t="s">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1281" t="s">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1282" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1283" t="s">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1284" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1285" t="s">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1287" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1288" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1289" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1290" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1292" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1293" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1294" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1296" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1298" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1299" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1300" t="s">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1301" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1302" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1303" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1304" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1305" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1306" t="s">
+        <v>4233</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1307" t="s">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1308" t="s">
+        <v>4235</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1309" t="s">
+        <v>4236</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1310" t="s">
+        <v>4237</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1311" t="s">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1312" t="s">
+        <v>4239</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1313" t="s">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1314" t="s">
+        <v>4241</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1315" t="s">
+        <v>4242</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1316" t="s">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1317" t="s">
+        <v>4244</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1318" t="s">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1319" t="s">
+        <v>4246</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1320" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1321" t="s">
+        <v>4248</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1322" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1323" t="s">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1324" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1325" t="s">
+        <v>4252</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1326" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1327" t="s">
+        <v>4254</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1328" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1329" t="s">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1330" t="s">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1331" t="s">
+        <v>4258</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1332" t="s">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1333" t="s">
+        <v>4260</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1334" t="s">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1335" t="s">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1336" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1337" t="s">
+        <v>4264</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1338" t="s">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1339" t="s">
+        <v>4266</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1340" t="s">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1341" t="s">
+        <v>4268</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1342" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1343" t="s">
+        <v>4270</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1344" t="s">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1345" t="s">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1346" t="s">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1347" t="s">
+        <v>4274</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1348" t="s">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1349" t="s">
+        <v>4276</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1350" t="s">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1351" t="s">
+        <v>4278</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1352" t="s">
+        <v>4279</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1353" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1354" t="s">
+        <v>4281</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1355" t="s">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1356" t="s">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1357" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1358" t="s">
+        <v>4285</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1359" t="s">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1360" t="s">
+        <v>4287</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1361" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1362" t="s">
+        <v>4289</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1363" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1364" t="s">
+        <v>4291</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1365" t="s">
+        <v>4292</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1366" t="s">
+        <v>4293</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1367" t="s">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1368" t="s">
+        <v>4295</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1369" t="s">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1370" t="s">
+        <v>4297</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1371" t="s">
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1372" t="s">
+        <v>4299</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1373" t="s">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1374" t="s">
+        <v>4301</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1375" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1376" t="s">
+        <v>4303</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1377" t="s">
+        <v>4304</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1378" t="s">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1379" t="s">
+        <v>4306</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1380" t="s">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1381" t="s">
+        <v>4308</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1382" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1383" t="s">
+        <v>4310</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1384" t="s">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1385" t="s">
+        <v>4312</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1386" t="s">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1387" t="s">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1388" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1389" t="s">
+        <v>4316</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1390" t="s">
+        <v>4317</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1391" t="s">
+        <v>4318</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1392" t="s">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1393" t="s">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1394" t="s">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1395" t="s">
+        <v>4322</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1396" t="s">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1397" t="s">
+        <v>4324</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1398" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1399" t="s">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1400" t="s">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1401" t="s">
+        <v>4328</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1402" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1403" t="s">
+        <v>4330</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1404" t="s">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1405" t="s">
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1406" t="s">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1407" t="s">
+        <v>4334</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1408" t="s">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1409" t="s">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1410" t="s">
+        <v>4337</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1411" t="s">
+        <v>4338</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1412" t="s">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1413" t="s">
+        <v>4340</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1414" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1415" t="s">
+        <v>4342</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1416" t="s">
+        <v>4343</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1417" t="s">
+        <v>4344</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1418" t="s">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1419" t="s">
+        <v>4346</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1420" t="s">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1421" t="s">
+        <v>4348</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1422" t="s">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1423" t="s">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1424" t="s">
+        <v>4351</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1425" t="s">
+        <v>4352</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1426" t="s">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1427" t="s">
+        <v>4354</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1428" t="s">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1429" t="s">
+        <v>4356</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1430" t="s">
+        <v>4357</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1431" t="s">
+        <v>4358</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1432" t="s">
+        <v>4359</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1433" t="s">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1434" t="s">
+        <v>4361</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1435" t="s">
+        <v>4362</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1436" t="s">
+        <v>4363</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1437" t="s">
+        <v>4364</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1438" t="s">
+        <v>4365</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1439" t="s">
+        <v>4366</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1440" t="s">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1441" t="s">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1442" t="s">
+        <v>4369</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1443" t="s">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1444" t="s">
+        <v>4371</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1445" t="s">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1446" t="s">
+        <v>4373</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1447" t="s">
+        <v>4374</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1448" t="s">
+        <v>4375</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1449" t="s">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1450" t="s">
+        <v>4377</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1451" t="s">
+        <v>4378</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1452" t="s">
+        <v>4379</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1453" t="s">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1454" t="s">
+        <v>4381</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1455" t="s">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1456" t="s">
+        <v>4383</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1457" t="s">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1458" t="s">
+        <v>4385</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1459" t="s">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1460" t="s">
+        <v>4387</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1461" t="s">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1463" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1464" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1465" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1466" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1468" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1469" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1470" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1472" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1474" t="s">
+        <v>4389</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1475" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1476" t="s">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1477" t="s">
+        <v>4391</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1478" t="s">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1479" t="s">
+        <v>4393</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1480" t="s">
+        <v>4394</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1481" t="s">
+        <v>4395</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1482" t="s">
+        <v>4396</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1483" t="s">
+        <v>4397</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1484" t="s">
+        <v>4398</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1485" t="s">
+        <v>4399</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1486" t="s">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1487" t="s">
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1488" t="s">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1489" t="s">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1490" t="s">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1491" t="s">
+        <v>4405</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1492" t="s">
+        <v>4406</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1493" t="s">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1494" t="s">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1495" t="s">
+        <v>4409</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1496" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1497" t="s">
+        <v>4411</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1498" t="s">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1499" t="s">
+        <v>4413</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1500" t="s">
+        <v>4414</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1501" t="s">
+        <v>4415</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1502" t="s">
+        <v>4416</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1503" t="s">
+        <v>4417</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1504" t="s">
+        <v>4418</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1505" t="s">
+        <v>4419</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1506" t="s">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1507" t="s">
+        <v>4421</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1508" t="s">
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1509" t="s">
+        <v>4423</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1510" t="s">
+        <v>4424</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1511" t="s">
+        <v>4425</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1512" t="s">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1513" t="s">
+        <v>4427</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1514" t="s">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1515" t="s">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1516" t="s">
+        <v>4430</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1517" t="s">
+        <v>4431</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1518" t="s">
+        <v>4432</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1519" t="s">
+        <v>4433</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1520" t="s">
+        <v>4434</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1521" t="s">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1522" t="s">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1523" t="s">
+        <v>4437</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1524" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1525" t="s">
+        <v>4439</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1526" t="s">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1527" t="s">
+        <v>4441</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1528" t="s">
+        <v>4442</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1529" t="s">
+        <v>4443</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1530" t="s">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1531" t="s">
+        <v>4445</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1532" t="s">
+        <v>4446</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1533" t="s">
+        <v>4447</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1534" t="s">
+        <v>4448</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1535" t="s">
+        <v>4449</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1536" t="s">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1537" t="s">
+        <v>4451</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1538" t="s">
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1539" t="s">
+        <v>4453</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1540" t="s">
+        <v>4454</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1541" t="s">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1542" t="s">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1543" t="s">
+        <v>4457</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1544" t="s">
+        <v>4458</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1545" t="s">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1546" t="s">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1547" t="s">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1548" t="s">
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1549" t="s">
+        <v>4463</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1550" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1551" t="s">
+        <v>4465</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1552" t="s">
+        <v>4466</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1553" t="s">
+        <v>4467</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1554" t="s">
+        <v>4468</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1555" t="s">
+        <v>4469</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1556" t="s">
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1557" t="s">
+        <v>4471</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1558" t="s">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1559" t="s">
+        <v>4473</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1560" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1561" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1562" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1563" t="s">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1564" t="s">
+        <v>4478</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1565" t="s">
+        <v>4479</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1566" t="s">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1567" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1568" t="s">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1569" t="s">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1570" t="s">
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1571" t="s">
+        <v>4485</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1572" t="s">
+        <v>4486</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1573" t="s">
+        <v>4487</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1574" t="s">
+        <v>4488</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1575" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1576" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1577" t="s">
+        <v>4491</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1578" t="s">
+        <v>4492</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1579" t="s">
+        <v>4493</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1580" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1581" t="s">
+        <v>4495</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1582" t="s">
+        <v>4496</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1583" t="s">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1584" t="s">
+        <v>4498</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1585" t="s">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1586" t="s">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1587" t="s">
+        <v>4501</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1588" t="s">
+        <v>4502</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1589" t="s">
+        <v>4503</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1590" t="s">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1591" t="s">
+        <v>4505</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1592" t="s">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1593" t="s">
+        <v>4507</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1594" t="s">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1595" t="s">
+        <v>4509</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1596" t="s">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1597" t="s">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1598" t="s">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1599" t="s">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1600" t="s">
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1601" t="s">
+        <v>4515</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1602" t="s">
+        <v>4516</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1603" t="s">
+        <v>4517</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1604" t="s">
+        <v>4518</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1605" t="s">
+        <v>4519</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1606" t="s">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1607" t="s">
+        <v>4521</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1608" t="s">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1609" t="s">
+        <v>4523</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1610" t="s">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1611" t="s">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1612" t="s">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1613" t="s">
+        <v>4527</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1614" t="s">
+        <v>4528</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1615" t="s">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1616" t="s">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1617" t="s">
+        <v>4531</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1618" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1619" t="s">
+        <v>4533</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1620" t="s">
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1621" t="s">
+        <v>4535</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1622" t="s">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1623" t="s">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1624" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1625" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1626" t="s">
+        <v>4540</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1627" t="s">
+        <v>4541</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1628" t="s">
+        <v>4542</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1629" t="s">
+        <v>4543</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1630" t="s">
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1631" t="s">
+        <v>4545</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1632" t="s">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1633" t="s">
+        <v>4547</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1634" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1635" t="s">
+        <v>4549</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1636" t="s">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1637" t="s">
+        <v>4551</v>
       </c>
     </row>
   </sheetData>
